--- a/Personal .xlsx
+++ b/Personal .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{8E962E59-1E3C-47E7-B657-D33E446696A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81282DB0-604C-43FC-9B04-3AC0E37A8FB8}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{8E962E59-1E3C-47E7-B657-D33E446696A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3E08C4C-D444-412C-98FD-7AEA4259E141}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="11" xr2:uid="{B4E95347-2E7C-4825-AC90-B7E638AE40C2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="24" xr2:uid="{B4E95347-2E7C-4825-AC90-B7E638AE40C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -25,19 +25,45 @@
     <sheet name="Referencia a otras hojas" sheetId="9" r:id="rId10"/>
     <sheet name="Formatos y Estilos  de celdas" sheetId="12" r:id="rId11"/>
     <sheet name="Formato Condicional" sheetId="13" r:id="rId12"/>
+    <sheet name="Insertar y eliminar" sheetId="14" r:id="rId13"/>
+    <sheet name="Ordenanr y Filtrar" sheetId="15" r:id="rId14"/>
+    <sheet name="Tablas Dinamica y Subtotales" sheetId="16" r:id="rId15"/>
+    <sheet name="Privot" sheetId="18" r:id="rId16"/>
+    <sheet name="Tablas Dinamica " sheetId="17" r:id="rId17"/>
+    <sheet name="Administrador" sheetId="29" r:id="rId18"/>
+    <sheet name="Contador" sheetId="28" r:id="rId19"/>
+    <sheet name="Logística" sheetId="27" r:id="rId20"/>
+    <sheet name="Secretaria" sheetId="26" r:id="rId21"/>
+    <sheet name="Femenino" sheetId="32" r:id="rId22"/>
+    <sheet name="Masculino" sheetId="31" r:id="rId23"/>
+    <sheet name="Filtro" sheetId="20" r:id="rId24"/>
+    <sheet name="Filtros Avanzado" sheetId="19" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v5.0" hidden="1">'Formato Condicional'!$H$5</definedName>
-    <definedName name="_xlchart.v5.1" hidden="1">'Formato Condicional'!$H$6:$H$14</definedName>
-    <definedName name="_xlchart.v5.2" hidden="1">'Formato Condicional'!$H$5</definedName>
-    <definedName name="_xlchart.v5.3" hidden="1">'Formato Condicional'!$H$6:$H$14</definedName>
-    <definedName name="_xlchart.v5.4" hidden="1">'Formato Condicional'!$H$5</definedName>
-    <definedName name="_xlchart.v5.5" hidden="1">'Formato Condicional'!$H$6:$H$14</definedName>
-    <definedName name="_xlchart.v5.6" hidden="1">'Formato Condicional'!$H$5</definedName>
-    <definedName name="_xlchart.v5.7" hidden="1">'Formato Condicional'!$H$6:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Filtros Avanzado'!$B$3:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ordenanr y Filtrar'!$B$3:$E$15</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="24">'Filtros Avanzado'!$I$3:$N$4</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="24">'Filtros Avanzado'!$I$25:$N$25</definedName>
+    <definedName name="Slicer_Producto">#N/A</definedName>
+    <definedName name="Slicer_Sucursal">#N/A</definedName>
+    <definedName name="Slicer_Vendedor">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="36" r:id="rId26"/>
+    <pivotCache cacheId="47" r:id="rId27"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId28"/>
+        <x14:slicerCache r:id="rId29"/>
+        <x14:slicerCache r:id="rId30"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -55,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="238">
   <si>
     <t xml:space="preserve"> Presupuesto Mensual</t>
   </si>
@@ -394,6 +420,381 @@
   </si>
   <si>
     <t xml:space="preserve">Productos tipo A hasta tipo F </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Producto 10</t>
+  </si>
+  <si>
+    <t>Producto 12</t>
+  </si>
+  <si>
+    <t>Producto 8</t>
+  </si>
+  <si>
+    <t>Producto 4</t>
+  </si>
+  <si>
+    <t>Producto 9</t>
+  </si>
+  <si>
+    <t>Producto 6</t>
+  </si>
+  <si>
+    <t>Producto 7</t>
+  </si>
+  <si>
+    <t>Producto 3</t>
+  </si>
+  <si>
+    <t>Producto 5</t>
+  </si>
+  <si>
+    <t>Producto 1</t>
+  </si>
+  <si>
+    <t>Producto 11</t>
+  </si>
+  <si>
+    <t>Producto 2</t>
+  </si>
+  <si>
+    <t>Sucursal</t>
+  </si>
+  <si>
+    <t>Vendedor</t>
+  </si>
+  <si>
+    <t>Ventas</t>
+  </si>
+  <si>
+    <t>Suc-3</t>
+  </si>
+  <si>
+    <t>Asociado-12</t>
+  </si>
+  <si>
+    <t>ID-10</t>
+  </si>
+  <si>
+    <t>Suc-1</t>
+  </si>
+  <si>
+    <t>Asociado-1</t>
+  </si>
+  <si>
+    <t>Suc-5</t>
+  </si>
+  <si>
+    <t>Asociado-27</t>
+  </si>
+  <si>
+    <t>ID-08</t>
+  </si>
+  <si>
+    <t>Suc-2</t>
+  </si>
+  <si>
+    <t>Asociado-7</t>
+  </si>
+  <si>
+    <t>ID-18</t>
+  </si>
+  <si>
+    <t>Suc-4</t>
+  </si>
+  <si>
+    <t>Asociado-21</t>
+  </si>
+  <si>
+    <t>ID-03</t>
+  </si>
+  <si>
+    <t>Asociado-10</t>
+  </si>
+  <si>
+    <t>ID-17</t>
+  </si>
+  <si>
+    <t>Asociado-31</t>
+  </si>
+  <si>
+    <t>ID-40</t>
+  </si>
+  <si>
+    <t>Asociado-4</t>
+  </si>
+  <si>
+    <t>ID-15</t>
+  </si>
+  <si>
+    <t>Asociado-18</t>
+  </si>
+  <si>
+    <t>ID-25</t>
+  </si>
+  <si>
+    <t>Asociado-11</t>
+  </si>
+  <si>
+    <t>ID-12</t>
+  </si>
+  <si>
+    <t>Asociado-13</t>
+  </si>
+  <si>
+    <t>ID-32</t>
+  </si>
+  <si>
+    <t>Asociado-22</t>
+  </si>
+  <si>
+    <t>ID-09</t>
+  </si>
+  <si>
+    <t>Asociado-8</t>
+  </si>
+  <si>
+    <t>ID-19</t>
+  </si>
+  <si>
+    <t>Asociado-2</t>
+  </si>
+  <si>
+    <t>ID-44</t>
+  </si>
+  <si>
+    <t>Asociado-16</t>
+  </si>
+  <si>
+    <t>ID-28</t>
+  </si>
+  <si>
+    <t>Asociado-17</t>
+  </si>
+  <si>
+    <t>ID-48</t>
+  </si>
+  <si>
+    <t>Asociado-29</t>
+  </si>
+  <si>
+    <t>ID-35</t>
+  </si>
+  <si>
+    <t>Asociado-6</t>
+  </si>
+  <si>
+    <t>ID-24</t>
+  </si>
+  <si>
+    <t>Asociado-14</t>
+  </si>
+  <si>
+    <t>ID-02</t>
+  </si>
+  <si>
+    <t>Asociado-9</t>
+  </si>
+  <si>
+    <t>ID-31</t>
+  </si>
+  <si>
+    <t>Asociado-19</t>
+  </si>
+  <si>
+    <t>ID-41</t>
+  </si>
+  <si>
+    <t>Asociado-3</t>
+  </si>
+  <si>
+    <t>ID-22</t>
+  </si>
+  <si>
+    <t>Asociado-15</t>
+  </si>
+  <si>
+    <t>ID-05</t>
+  </si>
+  <si>
+    <t>Asociado-24</t>
+  </si>
+  <si>
+    <t>Asociado-30</t>
+  </si>
+  <si>
+    <t>ID-39</t>
+  </si>
+  <si>
+    <t>Asociado-5</t>
+  </si>
+  <si>
+    <t>ID-20</t>
+  </si>
+  <si>
+    <t>Asociado-26</t>
+  </si>
+  <si>
+    <t>ID-14</t>
+  </si>
+  <si>
+    <t>Asociado-20</t>
+  </si>
+  <si>
+    <t>ID-33</t>
+  </si>
+  <si>
+    <t>Asociado-28</t>
+  </si>
+  <si>
+    <t>ID-07</t>
+  </si>
+  <si>
+    <t>Asociado-23</t>
+  </si>
+  <si>
+    <t>ID-45</t>
+  </si>
+  <si>
+    <t>Suc-1 Total</t>
+  </si>
+  <si>
+    <t>Suc-2 Total</t>
+  </si>
+  <si>
+    <t>Suc-3 Total</t>
+  </si>
+  <si>
+    <t>Suc-4 Total</t>
+  </si>
+  <si>
+    <t>Suc-5 Total</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Ventas</t>
+  </si>
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>Nombre y Apellido</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Sueldo</t>
+  </si>
+  <si>
+    <t>Miguel Vela</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Julio Martín</t>
+  </si>
+  <si>
+    <t>Miguel Sánchez</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>María Salcedo</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Lizeth Lozano</t>
+  </si>
+  <si>
+    <t>Mario Casas</t>
+  </si>
+  <si>
+    <t>José López</t>
+  </si>
+  <si>
+    <t>Contador</t>
+  </si>
+  <si>
+    <t>Marcia Cárdenas</t>
+  </si>
+  <si>
+    <t>Jean Carlos Larrea</t>
+  </si>
+  <si>
+    <t>Marleni Farisque</t>
+  </si>
+  <si>
+    <t>Secretaria</t>
+  </si>
+  <si>
+    <t>Sandra Cubas</t>
+  </si>
+  <si>
+    <t>Pedro Ramírez</t>
+  </si>
+  <si>
+    <t>Ana Pérez</t>
+  </si>
+  <si>
+    <t>Carlos Méndez</t>
+  </si>
+  <si>
+    <t>Rosa Jiménez</t>
+  </si>
+  <si>
+    <t>Luis Gómez</t>
+  </si>
+  <si>
+    <t>Diana Castillo</t>
+  </si>
+  <si>
+    <t>Andrés Torres</t>
+  </si>
+  <si>
+    <t>Patricia Medina</t>
+  </si>
+  <si>
+    <t>Kevin Díaz</t>
+  </si>
+  <si>
+    <t>Sofía Herrera</t>
+  </si>
+  <si>
+    <t>Cristian Núñez</t>
+  </si>
+  <si>
+    <t>Laura Ortiz</t>
+  </si>
+  <si>
+    <t>&gt;26</t>
+  </si>
+  <si>
+    <t>Sum of Sueldo</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Justino Baca</t>
   </si>
 </sst>
 </file>
@@ -403,12 +804,12 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="0.0000"/>
-    <numFmt numFmtId="176" formatCode="[$$-2C0A]\ #,##0.00;\-[$$-2C0A]\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="[$$-2C0A]\ #,##0.00;\-[$$-2C0A]\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,8 +892,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,8 +1004,43 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -701,8 +1158,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -712,8 +1180,10 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -745,16 +1215,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -762,7 +1225,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -802,29 +1264,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -843,43 +1292,114 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="17" borderId="1" xfId="10" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="16" borderId="1" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="11">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
     <cellStyle name="20% - Accent3" xfId="5" builtinId="38"/>
     <cellStyle name="20% - Accent6" xfId="3" builtinId="50"/>
     <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
     <cellStyle name="60% - Accent3" xfId="6" builtinId="40"/>
+    <cellStyle name="60% - Accent4" xfId="10" builtinId="44"/>
     <cellStyle name="60% - Accent6" xfId="4" builtinId="52"/>
     <cellStyle name="Accent2" xfId="8" builtinId="33"/>
+    <cellStyle name="Good" xfId="9" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Total" xfId="7" builtinId="25"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -900,10 +1420,34 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF5050"/>
       <color rgb="FF9999FF"/>
     </mruColors>
   </colors>
@@ -916,6 +1460,3123 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Personal .xlsx]Privot!Pivot1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Privot!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Privot!$A$4:$A$44</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="30"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Asociado-1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Asociado-10</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Asociado-13</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Asociado-17</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Asociado-19</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Asociado-5</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Asociado-22</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Asociado-26</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Asociado-29</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Asociado-3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Asociado-4</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Asociado-7</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Asociado-12</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Asociado-14</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>Asociado-18</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>Asociado-2</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>Asociado-24</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>Asociado-28</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>Asociado-11</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>Asociado-16</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>Asociado-21</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>Asociado-23</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>Asociado-30</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>Asociado-9</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>Asociado-15</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>Asociado-20</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>Asociado-27</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>Asociado-31</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>Asociado-6</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>Asociado-8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Suc-1</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Suc-2</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Suc-3</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>Suc-4</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>Suc-5</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Privot!$B$4:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>646</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>638</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>771</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>662</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>578</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>458</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>721</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>694</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>951</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>777</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>487</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>529</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>884</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>812</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>843</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>699</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>506</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>418</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>745</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D10-48E8-8791-1C9AFF5F7B38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="75"/>
+        <c:axId val="820992432"/>
+        <c:axId val="1266005456"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="820992432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266005456"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1266005456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="820992432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01EB8E5-EB5B-3B75-6A5C-AF9FD26CE37C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>112395</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Sucursal">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57AAA14E-CC5D-D45F-34D2-4513FD01FA37}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Sucursal"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1988820" y="22860"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>120015</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Vendedor">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16C7970D-8ED3-217E-A238-BA3FEA3C609B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Vendedor"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3909060" y="30480"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Producto">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6EF4D70-9EE2-D4FB-6609-C973C5D9B379}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Producto"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5806440" y="15240"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edwin" refreshedDate="46205.562547800924" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{E154FBAA-6CF6-4298-A64A-2AF5CBA78E00}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Sucursal" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Suc-1"/>
+        <s v="Suc-2"/>
+        <s v="Suc-3"/>
+        <s v="Suc-4"/>
+        <s v="Suc-5"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Vendedor" numFmtId="0">
+      <sharedItems count="30">
+        <s v="Asociado-1"/>
+        <s v="Asociado-10"/>
+        <s v="Asociado-13"/>
+        <s v="Asociado-17"/>
+        <s v="Asociado-19"/>
+        <s v="Asociado-5"/>
+        <s v="Asociado-7"/>
+        <s v="Asociado-4"/>
+        <s v="Asociado-22"/>
+        <s v="Asociado-29"/>
+        <s v="Asociado-3"/>
+        <s v="Asociado-26"/>
+        <s v="Asociado-12"/>
+        <s v="Asociado-18"/>
+        <s v="Asociado-2"/>
+        <s v="Asociado-14"/>
+        <s v="Asociado-24"/>
+        <s v="Asociado-28"/>
+        <s v="Asociado-21"/>
+        <s v="Asociado-11"/>
+        <s v="Asociado-16"/>
+        <s v="Asociado-9"/>
+        <s v="Asociado-30"/>
+        <s v="Asociado-23"/>
+        <s v="Asociado-27"/>
+        <s v="Asociado-31"/>
+        <s v="Asociado-8"/>
+        <s v="Asociado-6"/>
+        <s v="Asociado-15"/>
+        <s v="Asociado-20"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems count="28">
+        <s v="ID-10"/>
+        <s v="ID-17"/>
+        <s v="ID-32"/>
+        <s v="ID-48"/>
+        <s v="ID-41"/>
+        <s v="ID-20"/>
+        <s v="ID-18"/>
+        <s v="ID-15"/>
+        <s v="ID-09"/>
+        <s v="ID-35"/>
+        <s v="ID-22"/>
+        <s v="ID-14"/>
+        <s v="ID-25"/>
+        <s v="ID-44"/>
+        <s v="ID-02"/>
+        <s v="ID-07"/>
+        <s v="ID-03"/>
+        <s v="ID-12"/>
+        <s v="ID-28"/>
+        <s v="ID-31"/>
+        <s v="ID-39"/>
+        <s v="ID-45"/>
+        <s v="ID-08"/>
+        <s v="ID-40"/>
+        <s v="ID-19"/>
+        <s v="ID-24"/>
+        <s v="ID-05"/>
+        <s v="ID-33"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Ventas" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="226" maxValue="951"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="133540660"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Edwin" refreshedDate="46205.565373958336" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="24" xr:uid="{AF54E660-DC4D-4452-B2E5-F8918D28092D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B3:G27" sheet="Filtros Avanzado"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="DNI" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12548984" maxValue="56985968"/>
+    </cacheField>
+    <cacheField name="Nombre y Apellido" numFmtId="0">
+      <sharedItems count="24">
+        <s v="Miguel Vela"/>
+        <s v="Julio Martín"/>
+        <s v="Miguel Sánchez"/>
+        <s v="María Salcedo"/>
+        <s v="Lizeth Lozano"/>
+        <s v="Mario Casas"/>
+        <s v="José López"/>
+        <s v="Marcia Cárdenas"/>
+        <s v="Jean Carlos Larrea"/>
+        <s v="Marleni Farisque"/>
+        <s v="Sandra Cubas"/>
+        <s v="Pedro Ramírez"/>
+        <s v="Ana Pérez"/>
+        <s v="Carlos Méndez"/>
+        <s v="Rosa Jiménez"/>
+        <s v="Luis Gómez"/>
+        <s v="Diana Castillo"/>
+        <s v="Andrés Torres"/>
+        <s v="Patricia Medina"/>
+        <s v="Kevin Díaz"/>
+        <s v="Sofía Herrera"/>
+        <s v="Cristian Núñez"/>
+        <s v="Laura Ortiz"/>
+        <s v="Justino Baca"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sexo" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Masculino"/>
+        <s v="Femenino"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Edad" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="24" maxValue="45"/>
+    </cacheField>
+    <cacheField name="Cargo" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Administrador"/>
+        <s v="Logística"/>
+        <s v="Contador"/>
+        <s v="Secretaria"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sueldo" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1200" maxValue="3400"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="646"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="226"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="638"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="771"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="744"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="239"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="721"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="458"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="301"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="662"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="578"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="920"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="694"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="12"/>
+    <n v="777"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="13"/>
+    <n v="382"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <x v="14"/>
+    <n v="951"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="487"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="17"/>
+    <x v="15"/>
+    <n v="365"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="18"/>
+    <x v="16"/>
+    <n v="884"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="19"/>
+    <x v="17"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="20"/>
+    <x v="18"/>
+    <n v="529"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="19"/>
+    <n v="843"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="22"/>
+    <x v="20"/>
+    <n v="735"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="21"/>
+    <n v="812"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="24"/>
+    <x v="22"/>
+    <n v="532"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="25"/>
+    <x v="23"/>
+    <n v="615"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="26"/>
+    <x v="24"/>
+    <n v="745"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="27"/>
+    <x v="25"/>
+    <n v="418"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="28"/>
+    <x v="26"/>
+    <n v="699"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="29"/>
+    <x v="27"/>
+    <n v="506"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="24">
+  <r>
+    <n v="46250489"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="0"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <n v="25987456"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="0"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="15486325"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="31"/>
+    <x v="1"/>
+    <n v="2200"/>
+  </r>
+  <r>
+    <n v="12548984"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="29"/>
+    <x v="1"/>
+    <n v="2200"/>
+  </r>
+  <r>
+    <n v="56322588"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="27"/>
+    <x v="1"/>
+    <n v="2500"/>
+  </r>
+  <r>
+    <n v="44558874"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="40"/>
+    <x v="1"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <n v="43654785"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="45"/>
+    <x v="2"/>
+    <n v="1850"/>
+  </r>
+  <r>
+    <n v="56456564"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="2"/>
+    <n v="2850"/>
+  </r>
+  <r>
+    <n v="46548787"/>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="27"/>
+    <x v="2"/>
+    <n v="1850"/>
+  </r>
+  <r>
+    <n v="45465454"/>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="28"/>
+    <x v="3"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="56564654"/>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="27"/>
+    <x v="3"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="48974562"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="35"/>
+    <x v="0"/>
+    <n v="2600"/>
+  </r>
+  <r>
+    <n v="45879632"/>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="24"/>
+    <x v="3"/>
+    <n v="1300"/>
+  </r>
+  <r>
+    <n v="41236547"/>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="38"/>
+    <x v="1"/>
+    <n v="2750"/>
+  </r>
+  <r>
+    <n v="42365478"/>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="2"/>
+    <n v="2900"/>
+  </r>
+  <r>
+    <n v="49874563"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="29"/>
+    <x v="1"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="40125698"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="31"/>
+    <x v="3"/>
+    <n v="1450"/>
+  </r>
+  <r>
+    <n v="47896541"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="42"/>
+    <x v="0"/>
+    <n v="3400"/>
+  </r>
+  <r>
+    <n v="43215478"/>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="36"/>
+    <x v="2"/>
+    <n v="3100"/>
+  </r>
+  <r>
+    <n v="45698741"/>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="26"/>
+    <x v="1"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <n v="42147896"/>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="25"/>
+    <x v="3"/>
+    <n v="1250"/>
+  </r>
+  <r>
+    <n v="48796532"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="0"/>
+    <n v="3300"/>
+  </r>
+  <r>
+    <n v="46987412"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="2"/>
+    <n v="2950"/>
+  </r>
+  <r>
+    <n v="56985968"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="30"/>
+    <x v="0"/>
+    <n v="2500"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D27026A0-6AF4-40D2-97CE-C1E0A3FA8528}" name="Pivot1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0">
+      <items count="31">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item x="19"/>
+        <item x="12"/>
+        <item sd="0" x="2"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item sd="0" x="3"/>
+        <item x="13"/>
+        <item sd="0" x="4"/>
+        <item x="14"/>
+        <item x="29"/>
+        <item x="18"/>
+        <item x="8"/>
+        <item x="23"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="7"/>
+        <item sd="0" x="5"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item x="26"/>
+        <item x="21"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0">
+      <items count="29">
+        <item x="14"/>
+        <item x="16"/>
+        <item x="26"/>
+        <item x="15"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="2"/>
+        <item x="27"/>
+        <item x="9"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="41">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i t="default">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i t="default">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i t="default">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i t="default">
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Ventas" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable6" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable5" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable4" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" item="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable3" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" item="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable8" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable7" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="Pivot2" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A4:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="12"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Sucursal" xr10:uid="{B4AD0566-6644-4015-81E8-6279B0B9A96F}" sourceName="Sucursal">
+  <pivotTables>
+    <pivotTable tabId="18" name="Pivot1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="133540660">
+      <items count="5">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Vendedor" xr10:uid="{0F130614-2394-4828-84C1-CF544682A85E}" sourceName="Vendedor">
+  <pivotTables>
+    <pivotTable tabId="18" name="Pivot1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="133540660">
+      <items count="30">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="19" s="1"/>
+        <i x="12" s="1"/>
+        <i x="2" s="1"/>
+        <i x="15" s="1"/>
+        <i x="28" s="1"/>
+        <i x="20" s="1"/>
+        <i x="3" s="1"/>
+        <i x="13" s="1"/>
+        <i x="4" s="1"/>
+        <i x="14" s="1"/>
+        <i x="29" s="1"/>
+        <i x="18" s="1"/>
+        <i x="8" s="1"/>
+        <i x="23" s="1"/>
+        <i x="16" s="1"/>
+        <i x="11" s="1"/>
+        <i x="24" s="1"/>
+        <i x="17" s="1"/>
+        <i x="9" s="1"/>
+        <i x="10" s="1"/>
+        <i x="22" s="1"/>
+        <i x="25" s="1"/>
+        <i x="7" s="1"/>
+        <i x="5" s="1"/>
+        <i x="27" s="1"/>
+        <i x="6" s="1"/>
+        <i x="26" s="1"/>
+        <i x="21" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Producto" xr10:uid="{4A11452C-58B5-4C11-B15A-77B498F86D16}" sourceName="Producto">
+  <pivotTables>
+    <pivotTable tabId="18" name="Pivot1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="133540660">
+      <items count="28">
+        <i x="14" s="1"/>
+        <i x="16" s="1"/>
+        <i x="26" s="1"/>
+        <i x="15" s="1"/>
+        <i x="22" s="1"/>
+        <i x="8" s="1"/>
+        <i x="0" s="1"/>
+        <i x="17" s="1"/>
+        <i x="11" s="1"/>
+        <i x="7" s="1"/>
+        <i x="1" s="1"/>
+        <i x="6" s="1"/>
+        <i x="24" s="1"/>
+        <i x="5" s="1"/>
+        <i x="10" s="1"/>
+        <i x="25" s="1"/>
+        <i x="12" s="1"/>
+        <i x="18" s="1"/>
+        <i x="19" s="1"/>
+        <i x="2" s="1"/>
+        <i x="27" s="1"/>
+        <i x="9" s="1"/>
+        <i x="20" s="1"/>
+        <i x="23" s="1"/>
+        <i x="4" s="1"/>
+        <i x="13" s="1"/>
+        <i x="21" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Sucursal" xr10:uid="{BA63AB69-58D4-4091-B0E2-137C8B5A577B}" cache="Slicer_Sucursal" caption="Sucursal" rowHeight="234950"/>
+  <slicer name="Vendedor" xr10:uid="{C919B89F-D294-454C-97EF-363843983AEC}" cache="Slicer_Vendedor" caption="Vendedor" rowHeight="234950"/>
+  <slicer name="Producto" xr10:uid="{BB6E396B-D94F-4969-8220-A696610E5529}" cache="Slicer_Producto" caption="Producto" startItem="21" rowHeight="234950"/>
+</slicers>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD0CDE52-86FE-4F89-A6BD-70997E550C08}" name="Table1" displayName="Table1" ref="A1:D31" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:D31" xr:uid="{BD0CDE52-86FE-4F89-A6BD-70997E550C08}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8F830BF0-E0F2-4B12-9C7A-D79031A64DE9}" name="Sucursal"/>
+    <tableColumn id="2" xr3:uid="{72ED4F6A-CC1A-4FC2-8B5F-BA94E882656C}" name="Vendedor"/>
+    <tableColumn id="3" xr3:uid="{DF5D9482-E36A-4F9B-83D0-AE91B9E92BCC}" name="Producto"/>
+    <tableColumn id="4" xr3:uid="{7A3750FF-143E-497F-804C-0EA3382DEB58}" name="Ventas"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1222,14 +4883,15 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
@@ -1240,27 +4902,27 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="86" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="85">
         <v>12000</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="85"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
@@ -1268,10 +4930,10 @@
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="85">
         <v>4000</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="85"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -1279,10 +4941,10 @@
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="85">
         <v>6000</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="85"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
@@ -1290,8 +4952,8 @@
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="5">
+      <c r="B7" s="85"/>
+      <c r="C7" s="85">
         <v>400</v>
       </c>
       <c r="D7" s="1"/>
@@ -1301,8 +4963,8 @@
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5">
+      <c r="B8" s="85"/>
+      <c r="C8" s="85">
         <v>200</v>
       </c>
       <c r="D8" s="1"/>
@@ -1312,8 +4974,8 @@
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5">
+      <c r="B9" s="85"/>
+      <c r="C9" s="85">
         <v>100</v>
       </c>
       <c r="D9" s="1"/>
@@ -1323,8 +4985,8 @@
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85">
         <v>650</v>
       </c>
       <c r="D10" s="1"/>
@@ -1334,8 +4996,8 @@
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5">
+      <c r="B11" s="85"/>
+      <c r="C11" s="85">
         <v>350</v>
       </c>
       <c r="D11" s="1"/>
@@ -1345,8 +5007,8 @@
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="14">
+      <c r="B12" s="85"/>
+      <c r="C12" s="85">
         <v>2000</v>
       </c>
       <c r="D12" s="1"/>
@@ -1356,8 +5018,8 @@
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5">
+      <c r="B13" s="85"/>
+      <c r="C13" s="85">
         <v>300</v>
       </c>
       <c r="D13" s="1"/>
@@ -1367,8 +5029,8 @@
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="14">
+      <c r="B14" s="85"/>
+      <c r="C14" s="85">
         <v>1500</v>
       </c>
       <c r="D14" s="1"/>
@@ -1378,8 +5040,8 @@
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="14">
+      <c r="B15" s="85"/>
+      <c r="C15" s="85">
         <v>5000</v>
       </c>
       <c r="D15" s="1"/>
@@ -1389,8 +5051,8 @@
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5">
+      <c r="B16" s="85"/>
+      <c r="C16" s="85">
         <v>600</v>
       </c>
       <c r="D16" s="1"/>
@@ -1400,22 +5062,22 @@
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="14">
+      <c r="B17" s="85"/>
+      <c r="C17" s="85">
         <v>3000</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="88">
         <f>SUM(B4:B17)</f>
         <v>22000</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="87">
         <f>SUM(C7:C17)</f>
         <v>14100</v>
       </c>
@@ -1423,11 +5085,11 @@
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="16">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12">
         <f>B18-C18</f>
         <v>7900</v>
       </c>
@@ -1435,22 +5097,22 @@
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="13" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="17">
+      <c r="C20" s="14">
         <v>0.1</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="1">
+      <c r="C21" s="12">
         <f>C19-C19*C20</f>
         <v>7110</v>
       </c>
@@ -1493,7 +5155,70 @@
       <c r="E26" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C7:C17">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A3148EEB-4AA9-4072-9293-9A4001572457}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:B6">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD712278-0127-462F-9FB2-4D4E9A4481A7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A3148EEB-4AA9-4072-9293-9A4001572457}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C7:C17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DD712278-0127-462F-9FB2-4D4E9A4481A7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B4:B6</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1510,12 +5235,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1524,10 +5249,10 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="45" t="s">
         <v>108</v>
       </c>
       <c r="C3" s="1"/>
@@ -1537,7 +5262,7 @@
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="14">
         <v>0.02</v>
       </c>
       <c r="C4" s="1"/>
@@ -1547,7 +5272,7 @@
       <c r="A5" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="14">
         <v>0.03</v>
       </c>
       <c r="C5" s="1"/>
@@ -1557,7 +5282,7 @@
       <c r="A6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>0.05</v>
       </c>
       <c r="C6" s="1"/>
@@ -1567,7 +5292,7 @@
       <c r="A7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="44">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C7" s="1"/>
@@ -1577,7 +5302,7 @@
       <c r="A8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="14">
         <v>0.01</v>
       </c>
       <c r="C8" s="1"/>
@@ -1661,10 +5386,10 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="59" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1"/>
@@ -1676,17 +5401,17 @@
     <row r="5" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="55">
         <v>90</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="56">
         <v>1056870</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="I5" s="77" t="s">
@@ -1697,20 +5422,20 @@
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="51">
         <v>71</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="52">
         <v>1397706</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="16">
         <v>90</v>
       </c>
       <c r="I6" s="78">
@@ -1721,20 +5446,20 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="51">
         <v>61</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="52">
         <v>835212</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="16">
         <v>71</v>
       </c>
       <c r="I7" s="78">
@@ -1745,20 +5470,20 @@
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="53">
         <v>99</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="54">
         <v>1730124</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="16">
         <v>61</v>
       </c>
       <c r="I8" s="78">
@@ -1773,10 +5498,10 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="16">
         <v>99</v>
       </c>
       <c r="I9" s="78">
@@ -1789,7 +5514,7 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="58"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1799,11 +5524,11 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="72" t="s">
+      <c r="C11" s="57"/>
+      <c r="D11" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="63" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1"/>
@@ -1815,13 +5540,13 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="57">
         <v>90</v>
       </c>
-      <c r="E12" s="67">
+      <c r="E12" s="58">
         <v>1056870</v>
       </c>
       <c r="F12" s="1"/>
@@ -1833,13 +5558,13 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="57">
         <v>71</v>
       </c>
-      <c r="E13" s="67">
+      <c r="E13" s="58">
         <v>1397706</v>
       </c>
       <c r="F13" s="1"/>
@@ -1851,13 +5576,13 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="57">
         <v>61</v>
       </c>
-      <c r="E14" s="67">
+      <c r="E14" s="58">
         <v>835212</v>
       </c>
       <c r="F14" s="1"/>
@@ -1869,20 +5594,20 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="57">
         <v>99</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="58">
         <v>1730124</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="45"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -1935,6 +5660,9 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F67896-29CF-4801-A188-37BBE6538DA0}">
+  <sheetPr>
+    <tabColor rgb="FFFF5050"/>
+  </sheetPr>
   <dimension ref="A3:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1964,96 +5692,96 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="80" t="s">
+      <c r="D5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="81"/>
+      <c r="E5" s="70"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="59" t="s">
+      <c r="H5" s="50" t="s">
         <v>89</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="16">
         <v>90</v>
       </c>
-      <c r="D6" s="83">
+      <c r="D6" s="71">
         <v>1056870</v>
       </c>
-      <c r="E6" s="84"/>
+      <c r="E6" s="72"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="16">
         <v>59</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="16">
         <v>71</v>
       </c>
-      <c r="D7" s="83">
+      <c r="D7" s="71">
         <v>1397706</v>
       </c>
-      <c r="E7" s="84"/>
+      <c r="E7" s="72"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="16">
         <v>54</v>
       </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="16">
         <v>61</v>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="71">
         <v>835212</v>
       </c>
-      <c r="E8" s="84"/>
+      <c r="E8" s="72"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="79" t="s">
+      <c r="G8" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="16">
         <v>75</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="16">
         <v>99</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="71">
         <v>1730124</v>
       </c>
-      <c r="E9" s="84"/>
+      <c r="E9" s="72"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="79" t="s">
+      <c r="G9" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="16">
         <v>57</v>
       </c>
       <c r="I9" s="1"/>
@@ -2064,10 +5792,10 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="79" t="s">
+      <c r="G10" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="16">
         <v>63</v>
       </c>
       <c r="I10" s="1"/>
@@ -2078,10 +5806,10 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="16">
         <v>86</v>
       </c>
       <c r="I11" s="1"/>
@@ -2092,10 +5820,10 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="16">
         <v>100</v>
       </c>
       <c r="I12" s="1"/>
@@ -2106,10 +5834,10 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="16">
         <v>57</v>
       </c>
       <c r="I13" s="1"/>
@@ -2120,32 +5848,32 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="79" t="s">
+      <c r="G14" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="16">
         <v>54</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="79" t="s">
+      <c r="G15" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="16">
         <v>88</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -2154,8 +5882,8 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -2164,8 +5892,8 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2190,11 +5918,11 @@
     <mergeCell ref="D9:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:E9">
-    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>1000000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="greaterThan">
       <formula>" $ 1,282,668.00 "</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>1000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H15">
@@ -2234,6 +5962,1896 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C84FEB5-6FBA-4E19-B1FB-973B405F8BE0}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.34998626667073579"/>
+  </sheetPr>
+  <dimension ref="B1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="16">
+        <v>90</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="82">
+        <v>1056870</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="80"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="16">
+        <v>71</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="82">
+        <v>1397706</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="82">
+        <v>835212</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="79">
+        <v>61</v>
+      </c>
+      <c r="D9" s="79"/>
+      <c r="E9" s="82">
+        <v>1730124</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="16">
+        <v>99</v>
+      </c>
+      <c r="D10" s="81"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00729ABF-55BA-48AB-B0E3-9BC1E03E38C8}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B3:G16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="97">
+        <v>4</v>
+      </c>
+      <c r="D4" s="97">
+        <v>99</v>
+      </c>
+      <c r="E4" s="98">
+        <v>1730124</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="97">
+        <v>3</v>
+      </c>
+      <c r="D5" s="97">
+        <v>71</v>
+      </c>
+      <c r="E5" s="98">
+        <v>1218529</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="97">
+        <v>2</v>
+      </c>
+      <c r="D6" s="97">
+        <v>82</v>
+      </c>
+      <c r="E6" s="98">
+        <v>1579722</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="91">
+        <v>9</v>
+      </c>
+      <c r="D7" s="91">
+        <v>73</v>
+      </c>
+      <c r="E7" s="92">
+        <v>1662496</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="95">
+        <v>8</v>
+      </c>
+      <c r="D8" s="95">
+        <v>61</v>
+      </c>
+      <c r="E8" s="96">
+        <v>835212</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="95">
+        <v>7</v>
+      </c>
+      <c r="D9" s="95">
+        <v>63</v>
+      </c>
+      <c r="E9" s="96">
+        <v>1994467</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="91">
+        <v>6</v>
+      </c>
+      <c r="D10" s="91">
+        <v>77</v>
+      </c>
+      <c r="E10" s="92">
+        <v>1214288</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="91">
+        <v>5</v>
+      </c>
+      <c r="D11" s="91">
+        <v>79</v>
+      </c>
+      <c r="E11" s="92">
+        <v>1986729</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="91">
+        <v>12</v>
+      </c>
+      <c r="D12" s="91">
+        <v>71</v>
+      </c>
+      <c r="E12" s="92">
+        <v>1397706</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="91">
+        <v>11</v>
+      </c>
+      <c r="D13" s="91">
+        <v>66</v>
+      </c>
+      <c r="E13" s="92">
+        <v>781503</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="91">
+        <v>10</v>
+      </c>
+      <c r="D14" s="91">
+        <v>90</v>
+      </c>
+      <c r="E14" s="92">
+        <v>1056870</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="91">
+        <v>1</v>
+      </c>
+      <c r="D15" s="91">
+        <v>67</v>
+      </c>
+      <c r="E15" s="92">
+        <v>1335133</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B3:E15" xr:uid="{00729ABF-55BA-48AB-B0E3-9BC1E03E38C8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:E13">
+      <sortCondition sortBy="fontColor" ref="E3:E15" dxfId="3"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E15">
+    <sortCondition descending="1" ref="B4:B15"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A096CD0F-A30C-4A40-B434-AC75CD2815A7}">
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="1">
+        <v>646</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="1">
+        <v>226</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="1">
+        <v>638</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="1">
+        <v>771</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="1">
+        <v>744</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="1">
+        <v>239</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
+        <f>SUBTOTAL(9,D2:D7)</f>
+        <v>3264</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="1">
+        <v>301</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="1">
+        <v>920</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="1">
+        <v>662</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="1">
+        <v>578</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="1">
+        <v>458</v>
+      </c>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>721</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
+        <f>SUBTOTAL(9,D9:D14)</f>
+        <v>3640</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="1">
+        <v>694</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="1">
+        <v>951</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="1">
+        <v>777</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="1">
+        <v>382</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="1">
+        <v>487</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="1">
+        <v>365</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1">
+        <f>SUBTOTAL(9,D16:D21)</f>
+        <v>3656</v>
+      </c>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="1">
+        <v>690</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="1">
+        <v>529</v>
+      </c>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="1">
+        <v>884</v>
+      </c>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" s="1">
+        <v>812</v>
+      </c>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="1">
+        <v>735</v>
+      </c>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="1">
+        <v>843</v>
+      </c>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1">
+        <f>SUBTOTAL(9,D23:D28)</f>
+        <v>4493</v>
+      </c>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="1">
+        <v>699</v>
+      </c>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="1">
+        <v>506</v>
+      </c>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="1">
+        <v>532</v>
+      </c>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="1">
+        <v>615</v>
+      </c>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="1">
+        <v>418</v>
+      </c>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="1">
+        <v>745</v>
+      </c>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1">
+        <f>SUBTOTAL(9,D30:D35)</f>
+        <v>3515</v>
+      </c>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1">
+        <f>SUBTOTAL(9,D2:D35)</f>
+        <v>18568</v>
+      </c>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="40"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="40"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="40"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="40"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="40"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="40"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D35">
+    <sortCondition ref="A2:A35"/>
+    <sortCondition ref="B2:B35"/>
+    <sortCondition ref="C2:C35"/>
+  </sortState>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B82D84-792E-4E99-A4B9-D8DF7CB43D7A}">
+  <dimension ref="A3:B44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="102"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="102">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="102">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="102">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="103" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="102">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="103" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="102">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="102">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="102">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="102"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="103" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="102">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="103" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="102">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="103" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="102">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="102">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="102">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="103" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="102">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="101" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="102">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="102"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="103" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="102">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="103" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="102">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="103" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="102">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="103" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="102">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="102">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="102">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="101" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="102">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="102"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="103" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" s="102">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="103" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="102">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="102">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="103" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="102">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="102">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="102">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="101" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" s="102">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="102"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="102">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="103" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="102">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="103" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="102">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="102">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="103" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="102">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="103" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="102">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="101" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" s="102">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" s="102">
+        <v>18568</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6366CB-3E1F-4683-8C9B-5C2B886A2ABA}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31">
+        <v>506</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D31">
+    <sortCondition ref="A2:A31"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E6EE83-8E0E-4AD8-A50F-7D30CE59DC49}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="102">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="102">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="102">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="102">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="102">
+        <v>16600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1955EDC7-B961-4B79-862B-56184D1214F1}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="102">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="102">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="102">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="102">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="102">
+        <v>15500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06632B0F-E301-4613-876C-9996E1B47589}">
   <sheetPr>
@@ -2251,11 +7869,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -2568,6 +8186,1499 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782665E2-70FB-49E0-9CE8-FD03474A8975}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="102">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="102">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="102">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="102">
+        <v>17150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77255EB9-A96F-4454-95CC-2C0E7104C74B}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="102">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="102">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="102">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="102">
+        <v>6400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25245BDF-DBBD-4016-A6F3-C8695D55CF68}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="102">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="102">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="102">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="102">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="102">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="101" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="102">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="102">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="102">
+        <v>22900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB1DA1F-1B18-4336-B2F8-1A53211C66C7}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="102">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="102">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="102">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" s="102">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="102">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="102">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="101" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="101" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="101" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="102">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="101" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="102">
+        <v>32750</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3C97DA-5B59-4EF8-B2CD-9BCAFEBCB8FB}">
+  <dimension ref="A2:B29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="100" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="102">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="101" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="102">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="102">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="102">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="102">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="101" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="102">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="101" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="102">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="102">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="101" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" s="102">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="101" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="102">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="101" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="102">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="101" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="101" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="101" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="102">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="101" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" s="102">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="101" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" s="102">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="101" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="102">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="101" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="102">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="102">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="101" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" s="102">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="101" t="s">
+        <v>237</v>
+      </c>
+      <c r="B28" s="102">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="101" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="102">
+        <v>55650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53CA538-268F-4F51-BB9D-981C1ED66319}">
+  <dimension ref="B3:N30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="104" t="s">
+        <v>204</v>
+      </c>
+      <c r="I3" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="L3" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="N3" s="104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="16">
+        <v>46250489</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="16">
+        <v>32</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="16">
+        <v>3000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>206</v>
+      </c>
+      <c r="L4" t="s">
+        <v>234</v>
+      </c>
+      <c r="M4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="16">
+        <v>25987456</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="16">
+        <v>28</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="16">
+        <v>15486325</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="16">
+        <v>31</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G6" s="16">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="16">
+        <v>12548984</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="16">
+        <v>29</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" s="16">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="16">
+        <v>56322588</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="16">
+        <v>27</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G8" s="16">
+        <v>2500</v>
+      </c>
+      <c r="I8" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="K8" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="L8" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="N8" s="104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="16">
+        <v>44558874</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9" s="16">
+        <v>40</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="16">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="16">
+        <v>45465454</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L9" s="16">
+        <v>28</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N9" s="16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="16">
+        <v>43654785</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="16">
+        <v>45</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1850</v>
+      </c>
+      <c r="I10" s="16">
+        <v>40125698</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L10" s="16">
+        <v>31</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N10" s="16">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="16">
+        <v>56456564</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="16">
+        <v>30</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="16">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="16">
+        <v>46548787</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="16">
+        <v>27</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="16">
+        <v>45465454</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="16">
+        <v>28</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="16">
+        <v>56564654</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="16">
+        <v>27</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="16">
+        <v>48974562</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="16">
+        <v>35</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="16">
+        <v>2600</v>
+      </c>
+      <c r="I15" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="J15" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="L15" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" s="104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="16">
+        <v>45879632</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="16">
+        <v>24</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1300</v>
+      </c>
+      <c r="I16" s="16">
+        <v>45465454</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L16" s="16">
+        <v>28</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" s="16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="16">
+        <v>41236547</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="16">
+        <v>38</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="16">
+        <v>2750</v>
+      </c>
+      <c r="I17" s="16">
+        <v>56564654</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L17" s="16">
+        <v>27</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N17" s="16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="16">
+        <v>42365478</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="16">
+        <v>33</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="16">
+        <v>2900</v>
+      </c>
+      <c r="I18" s="16">
+        <v>45879632</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L18" s="16">
+        <v>24</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N18" s="16">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="16">
+        <v>49874563</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="16">
+        <v>29</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G19" s="16">
+        <v>2400</v>
+      </c>
+      <c r="I19" s="16">
+        <v>40125698</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L19" s="16">
+        <v>31</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N19" s="16">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="16">
+        <v>40125698</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E20" s="16">
+        <v>31</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G20" s="16">
+        <v>1450</v>
+      </c>
+      <c r="I20" s="16">
+        <v>42147896</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="L20" s="16">
+        <v>25</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="N20" s="16">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="16">
+        <v>47896541</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="16">
+        <v>42</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G21" s="16">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="16">
+        <v>43215478</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E22" s="16">
+        <v>36</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="16">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="16">
+        <v>45698741</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="16">
+        <v>26</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G23" s="16">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="16">
+        <v>42147896</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" s="16">
+        <v>25</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G24" s="16">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="16">
+        <v>48796532</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E25" s="16">
+        <v>39</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G25" s="16">
+        <v>3300</v>
+      </c>
+      <c r="I25" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="J25" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="K25" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="L25" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="N25" s="104" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="16">
+        <v>46987412</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E26" s="16">
+        <v>34</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" s="16">
+        <v>2950</v>
+      </c>
+      <c r="I26" s="16">
+        <v>46250489</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="L26" s="16">
+        <v>32</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N26" s="16">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="16">
+        <v>56985968</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="16">
+        <v>30</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G27" s="16">
+        <v>2500</v>
+      </c>
+      <c r="I27" s="16">
+        <v>25987456</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="L27" s="16">
+        <v>28</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N27" s="16">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="I28" s="16">
+        <v>48974562</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="L28" s="16">
+        <v>35</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N28" s="16">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="I29" s="16">
+        <v>47896541</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="L29" s="16">
+        <v>42</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N29" s="16">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="I30" s="16">
+        <v>48796532</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="L30" s="16">
+        <v>39</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N30" s="16">
+        <v>3300</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2595,16 +9706,16 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E3" s="1"/>
@@ -2612,17 +9723,17 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
+      <c r="A4" s="16">
         <v>10</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="16">
         <v>12</v>
       </c>
-      <c r="C4" s="20" t="b">
+      <c r="C4" s="17" t="b">
         <f>A4=B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="21" t="str">
+      <c r="D4" s="18" t="str">
         <f>IF(A4=B4, "Verdadero", "Falso")</f>
         <v>Falso</v>
       </c>
@@ -2631,17 +9742,17 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
+      <c r="A5" s="16">
         <v>20</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="16">
         <v>6</v>
       </c>
-      <c r="C5" s="22" t="b">
+      <c r="C5" s="19" t="b">
         <f>A5&gt;B5</f>
         <v>1</v>
       </c>
-      <c r="D5" s="23" t="str">
+      <c r="D5" s="20" t="str">
         <f>IF(A5&gt;=B5, "Verdadero", "Falso")</f>
         <v>Verdadero</v>
       </c>
@@ -2650,17 +9761,17 @@
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
+      <c r="A6" s="16">
         <v>30</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="16">
         <v>12</v>
       </c>
-      <c r="C6" s="20" t="b">
+      <c r="C6" s="17" t="b">
         <f>B6&gt;A6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="21" t="str">
+      <c r="D6" s="18" t="str">
         <f>IF(A6&lt;=B6, "Verdadero", "Falso")</f>
         <v>Falso</v>
       </c>
@@ -2669,17 +9780,17 @@
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
+      <c r="A7" s="16">
         <v>40</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="16">
         <v>16</v>
       </c>
-      <c r="C7" s="22" t="b">
+      <c r="C7" s="19" t="b">
         <f>A7&lt;&gt;B7</f>
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="str">
+      <c r="D7" s="20" t="str">
         <f>IF(A7&lt;&gt;B7, "Verdadero", "Falso")</f>
         <v>Verdadero</v>
       </c>
@@ -2754,23 +9865,23 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="21" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="1"/>
@@ -2784,17 +9895,17 @@
       <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <v>25</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="36" t="str">
+      <c r="H4" s="32" t="str">
         <f>LOOKUP(G4,B4:B13,C4:C13)</f>
         <v>Juan Perez</v>
       </c>
@@ -2809,17 +9920,17 @@
       <c r="C5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <v>45</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="25" t="s">
         <v>59</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="38" t="str">
+      <c r="H5" s="34" t="str">
         <f>LOOKUP(G5,B5:B14,C5:C14)</f>
         <v>Andres Sanchez</v>
       </c>
@@ -2834,17 +9945,17 @@
       <c r="C6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="24">
         <v>34</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="25" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="36" t="str">
+      <c r="H6" s="32" t="str">
         <f t="shared" ref="H6:H14" si="0">LOOKUP(G6,B6:B15,C6:C15)</f>
         <v>Mario Gonzalez</v>
       </c>
@@ -2859,17 +9970,17 @@
       <c r="C7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="24">
         <v>34</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="25" t="s">
         <v>62</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="38" t="str">
+      <c r="H7" s="34" t="str">
         <f t="shared" si="0"/>
         <v>María Dominguez</v>
       </c>
@@ -2884,17 +9995,17 @@
       <c r="C8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="24">
         <v>23</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="25" t="s">
         <v>67</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="36" t="str">
+      <c r="H8" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Juana Velez</v>
       </c>
@@ -2909,17 +10020,17 @@
       <c r="C9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="24">
         <v>54</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="25" t="s">
         <v>70</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="38" t="str">
+      <c r="H9" s="34" t="str">
         <f t="shared" si="0"/>
         <v>Pedro Urdiales</v>
       </c>
@@ -2934,17 +10045,17 @@
       <c r="C10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="24">
         <v>47</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="25" t="s">
         <v>73</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="36" t="str">
+      <c r="H10" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Samanta Loja</v>
       </c>
@@ -2959,17 +10070,17 @@
       <c r="C11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="24">
         <v>42</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="25" t="s">
         <v>76</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="38" t="str">
+      <c r="H11" s="34" t="str">
         <f t="shared" si="0"/>
         <v>Melina Lima</v>
       </c>
@@ -2984,17 +10095,17 @@
       <c r="C12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="24">
         <v>37</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="25" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="36" t="str">
+      <c r="H12" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Melisa Ruales</v>
       </c>
@@ -3009,17 +10120,17 @@
       <c r="C13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="24">
         <v>35</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="25" t="s">
         <v>82</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="H13" s="38" t="str">
+      <c r="H13" s="34" t="str">
         <f t="shared" si="0"/>
         <v>Esteban Arredondo</v>
       </c>
@@ -3087,59 +10198,59 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="28" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <v>25</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="24" t="s">
         <v>56</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="36">
         <f>VLOOKUP(G5,B5:E14,3,0)</f>
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="24">
         <v>45</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="24" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="1"/>
@@ -3152,38 +10263,38 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="24">
         <v>34</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="24" t="s">
         <v>62</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="24">
         <v>34</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="24" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="1"/>
@@ -3196,38 +10307,38 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="24">
         <v>23</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="24" t="s">
         <v>67</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="36">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="24">
         <v>54</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="24" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="1"/>
@@ -3240,38 +10351,38 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="24">
         <v>47</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="24" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="36">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="24">
         <v>42</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="24" t="s">
         <v>76</v>
       </c>
       <c r="F12" s="1"/>
@@ -3284,38 +10395,38 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="24">
         <v>37</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="24" t="s">
         <v>79</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="36">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="24">
         <v>35</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="24" t="s">
         <v>82</v>
       </c>
       <c r="F14" s="1"/>
@@ -3406,145 +10517,145 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="30" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="30" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="24">
         <v>25</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="24">
         <v>45</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="24">
         <v>34</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="24">
         <v>34</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="24">
         <v>23</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="24">
         <v>54</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="24">
         <v>47</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="24">
         <v>42</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="24">
         <v>37</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="24">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="24" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3564,7 +10675,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="28" t="s">
         <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -3584,7 +10695,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="28" t="s">
         <v>84</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -3763,23 +10874,23 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="39" t="s">
         <v>84</v>
       </c>
       <c r="I4" s="1"/>
@@ -3787,16 +10898,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <v>25</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="24" t="s">
         <v>56</v>
       </c>
       <c r="F5" s="1"/>
@@ -3812,16 +10923,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="24">
         <v>45</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="24" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="1"/>
@@ -3837,16 +10948,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="24">
         <v>34</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="24" t="s">
         <v>62</v>
       </c>
       <c r="F7" s="1"/>
@@ -3862,16 +10973,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="24">
         <v>34</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="24" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="1"/>
@@ -3887,16 +10998,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="24">
         <v>23</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="24" t="s">
         <v>67</v>
       </c>
       <c r="F9" s="1"/>
@@ -3912,16 +11023,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="24">
         <v>54</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="24" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="1"/>
@@ -3937,16 +11048,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="24">
         <v>47</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="24" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="1"/>
@@ -3962,16 +11073,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="24">
         <v>42</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="24" t="s">
         <v>76</v>
       </c>
       <c r="F12" s="1"/>
@@ -3987,16 +11098,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="24">
         <v>37</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="24" t="s">
         <v>79</v>
       </c>
       <c r="F13" s="1"/>
@@ -4014,16 +11125,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="24">
         <v>35</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="24" t="s">
         <v>82</v>
       </c>
       <c r="F14" s="1"/>
@@ -4068,7 +11179,10 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <f>_xlfn.XLOOKUP(G5,B5:B14,E5:E14,0)</f>
+        <v>0</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -4097,32 +11211,32 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="53"/>
+      <c r="D4" s="74"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="48">
         <v>0.08</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="48">
         <v>0.18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="48">
         <v>0.19</v>
       </c>
     </row>
@@ -4160,13 +11274,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -4182,150 +11296,150 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="41" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="16">
         <v>10</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="16">
         <v>10</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="16">
         <v>100</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="46">
         <f>D4*'Referencia a otras hojas'!$B$5</f>
         <v>3</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="16">
         <v>20</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="16">
         <v>25</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="16">
         <v>500</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="46">
         <f>D5*'Referencia a otras hojas'!$B$5</f>
         <v>15</v>
       </c>
-      <c r="F5" s="19"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="16">
         <v>5</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="16">
         <v>13</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="16">
         <v>65</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="46">
         <f>D6*'Referencia a otras hojas'!$B$5</f>
         <v>1.95</v>
       </c>
-      <c r="F6" s="19"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="16">
         <v>12</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="16">
         <v>500</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="16">
         <v>6</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="46">
         <f>D7*'Referencia a otras hojas'!$B$5</f>
         <v>0.18</v>
       </c>
-      <c r="F7" s="19"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="16">
         <v>50</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="16">
         <v>2.8</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="16">
         <v>140</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="46">
         <f>D8*'Referencia a otras hojas'!$B$5</f>
         <v>4.2</v>
       </c>
-      <c r="F8" s="19"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="16">
         <v>10</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="16">
         <v>1</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="16">
         <v>10</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="46">
         <f>D9*'Referencia a otras hojas'!$B$5</f>
         <v>0.3</v>
       </c>
-      <c r="F9" s="19"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
@@ -4340,54 +11454,54 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="42">
         <v>10</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="49">
         <v>25</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="42">
         <v>13</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="43">
         <v>500</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="43">
         <v>2800</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="43">
         <v>1000</v>
       </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="42">
         <f>B11*INTERMEDIO!$D$7</f>
         <v>1.9</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="42">
         <f>C11*INTERMEDIO!$D$7</f>
         <v>4.75</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="42">
         <f>D11*INTERMEDIO!$D$7</f>
         <v>2.4700000000000002</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="42">
         <f>E11*INTERMEDIO!$D$7</f>
         <v>95</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="42">
         <f>F11*INTERMEDIO!$D$7</f>
         <v>532</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="42">
         <f>G11*INTERMEDIO!$D$7</f>
         <v>190</v>
       </c>

--- a/Personal .xlsx
+++ b/Personal .xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{8E962E59-1E3C-47E7-B657-D33E446696A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3E08C4C-D444-412C-98FD-7AEA4259E141}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{8E962E59-1E3C-47E7-B657-D33E446696A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36EAF65A-4384-4DD2-AABF-67DA6321A4E5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="24" xr2:uid="{B4E95347-2E7C-4825-AC90-B7E638AE40C2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="21" xr2:uid="{B4E95347-2E7C-4825-AC90-B7E638AE40C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -30,35 +30,38 @@
     <sheet name="Tablas Dinamica y Subtotales" sheetId="16" r:id="rId15"/>
     <sheet name="Privot" sheetId="18" r:id="rId16"/>
     <sheet name="Tablas Dinamica " sheetId="17" r:id="rId17"/>
-    <sheet name="Administrador" sheetId="29" r:id="rId18"/>
-    <sheet name="Contador" sheetId="28" r:id="rId19"/>
-    <sheet name="Logística" sheetId="27" r:id="rId20"/>
-    <sheet name="Secretaria" sheetId="26" r:id="rId21"/>
-    <sheet name="Femenino" sheetId="32" r:id="rId22"/>
-    <sheet name="Masculino" sheetId="31" r:id="rId23"/>
-    <sheet name="Filtro" sheetId="20" r:id="rId24"/>
-    <sheet name="Filtros Avanzado" sheetId="19" r:id="rId25"/>
+    <sheet name="Filtro" sheetId="20" r:id="rId18"/>
+    <sheet name="Filtros Avanzado" sheetId="19" r:id="rId19"/>
+    <sheet name="Asignar nombres a celdas" sheetId="33" r:id="rId20"/>
+    <sheet name="Inmovilizar paneles" sheetId="36" r:id="rId21"/>
+    <sheet name="Graficos" sheetId="37" r:id="rId22"/>
+    <sheet name="Hoja6" sheetId="38" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Filtros Avanzado'!$B$3:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Filtros Avanzado'!$B$3:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ordenanr y Filtrar'!$B$3:$E$15</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="24">'Filtros Avanzado'!$I$3:$N$4</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="24">'Filtros Avanzado'!$I$25:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Presupuesto!$A$3:$C$21</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="18">'Filtros Avanzado'!$I$25:$N$25</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="18">'Filtros Avanzado'!$I$3:$N$4</definedName>
+    <definedName name="Gasto">Presupuesto!$C$18</definedName>
+    <definedName name="Gastos">'Asignar nombres a celdas'!$D$5</definedName>
+    <definedName name="Ingresos">Presupuesto!$B$18</definedName>
+    <definedName name="Producto">'Asignar nombres a celdas'!$C$5</definedName>
     <definedName name="Slicer_Producto">#N/A</definedName>
     <definedName name="Slicer_Sucursal">#N/A</definedName>
     <definedName name="Slicer_Vendedor">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId26"/>
-    <pivotCache cacheId="47" r:id="rId27"/>
+    <pivotCache cacheId="0" r:id="rId24"/>
+    <pivotCache cacheId="1" r:id="rId25"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
+        <x14:slicerCache r:id="rId26"/>
+        <x14:slicerCache r:id="rId27"/>
         <x14:slicerCache r:id="rId28"/>
-        <x14:slicerCache r:id="rId29"/>
-        <x14:slicerCache r:id="rId30"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -81,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="275">
   <si>
     <t xml:space="preserve"> Presupuesto Mensual</t>
   </si>
@@ -795,21 +798,133 @@
   </si>
   <si>
     <t>Justino Baca</t>
+  </si>
+  <si>
+    <t>Gastos 1</t>
+  </si>
+  <si>
+    <t>Gastos 2</t>
+  </si>
+  <si>
+    <t>Gastos 3</t>
+  </si>
+  <si>
+    <t>Gastos 4</t>
+  </si>
+  <si>
+    <t>Gastos 5</t>
+  </si>
+  <si>
+    <t>Gastos 6</t>
+  </si>
+  <si>
+    <t>Gastos 7</t>
+  </si>
+  <si>
+    <t>Producto 13</t>
+  </si>
+  <si>
+    <t>Producto 14</t>
+  </si>
+  <si>
+    <t>Producto 15</t>
+  </si>
+  <si>
+    <t>Producto 16</t>
+  </si>
+  <si>
+    <t>Producto 17</t>
+  </si>
+  <si>
+    <t>Producto 18</t>
+  </si>
+  <si>
+    <t>Producto 19</t>
+  </si>
+  <si>
+    <t>Producto 20</t>
+  </si>
+  <si>
+    <t>Producto 21</t>
+  </si>
+  <si>
+    <t>Producto 22</t>
+  </si>
+  <si>
+    <t>Producto 23</t>
+  </si>
+  <si>
+    <t>Producto 24</t>
+  </si>
+  <si>
+    <t>Producto 25</t>
+  </si>
+  <si>
+    <t>Producto 26</t>
+  </si>
+  <si>
+    <t>Producto 27</t>
+  </si>
+  <si>
+    <t>Producto 28</t>
+  </si>
+  <si>
+    <t>Producto 29</t>
+  </si>
+  <si>
+    <t>Producto 30</t>
+  </si>
+  <si>
+    <t>Llantas</t>
+  </si>
+  <si>
+    <t>Semanas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rines </t>
+  </si>
+  <si>
+    <t>Sem 1</t>
+  </si>
+  <si>
+    <t>Sem 2</t>
+  </si>
+  <si>
+    <t>Sem 3</t>
+  </si>
+  <si>
+    <t>Sem 4</t>
+  </si>
+  <si>
+    <t>VENTAS</t>
+  </si>
+  <si>
+    <t>Sem 5</t>
+  </si>
+  <si>
+    <t>Ventas por Categoria</t>
+  </si>
+  <si>
+    <t>Ventas Semanales Toatles</t>
+  </si>
+  <si>
+    <t>Distribuccion de las categorias</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="[$$-2C0A]\ #,##0.00;\-[$$-2C0A]\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -913,8 +1028,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,8 +1169,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1169,8 +1315,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1182,8 +1367,10 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1294,50 +1481,13 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1380,22 +1530,107 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="10" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="11" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="11">
-    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
-    <cellStyle name="20% - Accent3" xfId="5" builtinId="38"/>
-    <cellStyle name="20% - Accent6" xfId="3" builtinId="50"/>
-    <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
-    <cellStyle name="60% - Accent3" xfId="6" builtinId="40"/>
-    <cellStyle name="60% - Accent4" xfId="10" builtinId="44"/>
-    <cellStyle name="60% - Accent6" xfId="4" builtinId="52"/>
-    <cellStyle name="Accent2" xfId="8" builtinId="33"/>
-    <cellStyle name="Good" xfId="9" builtinId="26"/>
+  <cellStyles count="13">
+    <cellStyle name="20% - Énfasis1" xfId="1" builtinId="30"/>
+    <cellStyle name="20% - Énfasis3" xfId="5" builtinId="38"/>
+    <cellStyle name="20% - Énfasis6" xfId="3" builtinId="50"/>
+    <cellStyle name="60% - Énfasis1" xfId="2" builtinId="32"/>
+    <cellStyle name="60% - Énfasis3" xfId="6" builtinId="40"/>
+    <cellStyle name="60% - Énfasis4" xfId="10" builtinId="44"/>
+    <cellStyle name="60% - Énfasis6" xfId="4" builtinId="52"/>
+    <cellStyle name="Bueno" xfId="9" builtinId="26"/>
+    <cellStyle name="Celda de comprobación" xfId="12" builtinId="23"/>
+    <cellStyle name="Énfasis2" xfId="8" builtinId="33"/>
+    <cellStyle name="Neutral" xfId="11" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Total" xfId="7" builtinId="25"/>
   </cellStyles>
@@ -1465,7 +1700,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2052,9 +2287,1190 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Ventas por Categoría</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19399175781760308"/>
+          <c:y val="4.7534088726714031E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graficos!$C$3:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Llantas</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Rines </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graficos!$C$9:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>317</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C7B4-4DAD-A191-696AFE1680E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1962459599"/>
+        <c:axId val="1424019183"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1962459599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1424019183"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1424019183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962459599"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Ventas Semanales </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graficos!$B$4:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Sem 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sem 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sem 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sem 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sem 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graficos!$E$4:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>116</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB65-44AC-A612-661B861C78D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1962499039"/>
+        <c:axId val="1619211599"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1962499039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1619211599"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1619211599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1962499039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100"/>
+              <a:t>% de Ventas Por Categoría</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27428126716718548"/>
+          <c:y val="0.2318298175691002"/>
+          <c:w val="0.49505390843057939"/>
+          <c:h val="0.66334418891689528"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C5AC-4810-AF1A-826E299DBD10}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="inEnd"/>
+              <c:showLegendKey val="1"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-C5AC-4810-AF1A-826E299DBD10}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="1"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graficos!$C$3:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Llantas</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Rines </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graficos!$C$9:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>317</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C5AC-4810-AF1A-826E299DBD10}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24741222886251266"/>
+          <c:y val="0.88566313470075497"/>
+          <c:w val="0.54129987613907815"/>
+          <c:h val="7.9085156848311786E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -2561,6 +3977,1544 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2612,8 +5566,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>112395</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Sucursal">
@@ -2636,7 +5590,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2690,8 +5644,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>120015</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Vendedor">
@@ -2714,7 +5668,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2768,8 +5722,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Producto">
@@ -2792,7 +5746,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2831,6 +5785,119 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>308610</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5042F1F-7EBB-401C-0646-1DF01C64BB79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE44A44-4E1D-7AB9-DC08-BB099A729C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D736C9D-5B3E-6606-8228-D5FEBB79AA01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3378,7 +6445,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D27026A0-6AF4-40D2-97CE-C1E0A3FA8528}" name="Pivot1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D27026A0-6AF4-40D2-97CE-C1E0A3FA8528}" name="Pivot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" subtotalTop="0" showAll="0">
@@ -3620,687 +6687,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable6" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable5" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" item="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable4" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" item="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable3" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable8" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="2" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="PivotTable7" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="12"/>
-        <item x="17"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="10"/>
-        <item x="20"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="2" item="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Sueldo" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="Pivot2" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46A84B65-D182-4F43-A0B7-8E335B212C6C}" name="Pivot2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A4:B29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -4580,7 +6967,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4880,18 +7267,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
@@ -4903,13 +7290,13 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="73" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1"/>
@@ -4919,10 +7306,10 @@
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="85">
+      <c r="B4" s="72">
         <v>12000</v>
       </c>
-      <c r="C4" s="85"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
@@ -4930,10 +7317,10 @@
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="85">
+      <c r="B5" s="72">
         <v>4000</v>
       </c>
-      <c r="C5" s="85"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -4941,10 +7328,10 @@
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="72">
         <v>6000</v>
       </c>
-      <c r="C6" s="85"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
@@ -4952,8 +7339,8 @@
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85">
+      <c r="B7" s="72"/>
+      <c r="C7" s="72">
         <v>400</v>
       </c>
       <c r="D7" s="1"/>
@@ -4963,8 +7350,8 @@
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="85">
+      <c r="B8" s="72"/>
+      <c r="C8" s="72">
         <v>200</v>
       </c>
       <c r="D8" s="1"/>
@@ -4974,8 +7361,8 @@
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85">
+      <c r="B9" s="72"/>
+      <c r="C9" s="72">
         <v>100</v>
       </c>
       <c r="D9" s="1"/>
@@ -4985,8 +7372,8 @@
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85">
+      <c r="B10" s="72"/>
+      <c r="C10" s="72">
         <v>650</v>
       </c>
       <c r="D10" s="1"/>
@@ -4996,8 +7383,8 @@
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85">
+      <c r="B11" s="72"/>
+      <c r="C11" s="72">
         <v>350</v>
       </c>
       <c r="D11" s="1"/>
@@ -5007,8 +7394,8 @@
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85">
+      <c r="B12" s="72"/>
+      <c r="C12" s="72">
         <v>2000</v>
       </c>
       <c r="D12" s="1"/>
@@ -5018,8 +7405,8 @@
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85">
+      <c r="B13" s="72"/>
+      <c r="C13" s="72">
         <v>300</v>
       </c>
       <c r="D13" s="1"/>
@@ -5029,8 +7416,8 @@
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85">
+      <c r="B14" s="72"/>
+      <c r="C14" s="72">
         <v>1500</v>
       </c>
       <c r="D14" s="1"/>
@@ -5040,8 +7427,8 @@
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85">
+      <c r="B15" s="72"/>
+      <c r="C15" s="72">
         <v>5000</v>
       </c>
       <c r="D15" s="1"/>
@@ -5051,8 +7438,8 @@
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="85"/>
-      <c r="C16" s="85">
+      <c r="B16" s="72"/>
+      <c r="C16" s="72">
         <v>600</v>
       </c>
       <c r="D16" s="1"/>
@@ -5062,8 +7449,8 @@
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85">
+      <c r="B17" s="72"/>
+      <c r="C17" s="72">
         <v>3000</v>
       </c>
       <c r="D17" s="1"/>
@@ -5073,11 +7460,11 @@
       <c r="A18" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="88">
+      <c r="B18" s="75">
         <f>SUM(B4:B17)</f>
         <v>22000</v>
       </c>
-      <c r="C18" s="87">
+      <c r="C18" s="74">
         <f>SUM(C7:C17)</f>
         <v>14100</v>
       </c>
@@ -5155,9 +7542,24 @@
       <c r="E26" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:C21" xr:uid="{E417526C-63EF-4A09-BF7A-3CE1A17BEC30}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B4:B6">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD712278-0127-462F-9FB2-4D4E9A4481A7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C7:C17">
     <cfRule type="dataBar" priority="2">
       <dataBar>
@@ -5172,24 +7574,23 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B6">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DD712278-0127-462F-9FB2-4D4E9A4481A7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DD712278-0127-462F-9FB2-4D4E9A4481A7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B4:B6</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A3148EEB-4AA9-4072-9293-9A4001572457}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -5203,19 +7604,6 @@
           </x14:cfRule>
           <xm:sqref>C7:C17</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DD712278-0127-462F-9FB2-4D4E9A4481A7}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>B4:B6</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -5228,19 +7616,19 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5338,7 +7726,7 @@
     <tabColor rgb="FF9999FF"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -5414,10 +7802,10 @@
       <c r="H5" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="77" t="s">
+      <c r="I5" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="77"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -5438,10 +7826,10 @@
       <c r="H6" s="16">
         <v>90</v>
       </c>
-      <c r="I6" s="78">
+      <c r="I6" s="97">
         <v>1056870</v>
       </c>
-      <c r="J6" s="78"/>
+      <c r="J6" s="97"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -5462,10 +7850,10 @@
       <c r="H7" s="16">
         <v>71</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="97">
         <v>1397706</v>
       </c>
-      <c r="J7" s="78"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -5486,10 +7874,10 @@
       <c r="H8" s="16">
         <v>61</v>
       </c>
-      <c r="I8" s="78">
+      <c r="I8" s="97">
         <v>835212</v>
       </c>
-      <c r="J8" s="78"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5504,10 +7892,10 @@
       <c r="H9" s="16">
         <v>99</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="97">
         <v>1730124</v>
       </c>
-      <c r="J9" s="78"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -5664,7 +8052,7 @@
     <tabColor rgb="FFFF5050"/>
   </sheetPr>
   <dimension ref="A3:I21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
@@ -5695,10 +8083,10 @@
       <c r="C5" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="70"/>
+      <c r="E5" s="100"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="50" t="s">
@@ -5713,10 +8101,10 @@
       <c r="C6" s="16">
         <v>90</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="101">
         <v>1056870</v>
       </c>
-      <c r="E6" s="72"/>
+      <c r="E6" s="102"/>
       <c r="F6" s="1"/>
       <c r="G6" s="67" t="s">
         <v>88</v>
@@ -5733,10 +8121,10 @@
       <c r="C7" s="16">
         <v>71</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="101">
         <v>1397706</v>
       </c>
-      <c r="E7" s="72"/>
+      <c r="E7" s="102"/>
       <c r="F7" s="1"/>
       <c r="G7" s="67" t="s">
         <v>88</v>
@@ -5753,10 +8141,10 @@
       <c r="C8" s="16">
         <v>61</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="101">
         <v>835212</v>
       </c>
-      <c r="E8" s="72"/>
+      <c r="E8" s="102"/>
       <c r="F8" s="1"/>
       <c r="G8" s="67" t="s">
         <v>88</v>
@@ -5773,10 +8161,10 @@
       <c r="C9" s="16">
         <v>99</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="101">
         <v>1730124</v>
       </c>
-      <c r="E9" s="72"/>
+      <c r="E9" s="102"/>
       <c r="F9" s="1"/>
       <c r="G9" s="67" t="s">
         <v>88</v>
@@ -5858,8 +8246,8 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="67" t="s">
@@ -5872,8 +8260,8 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -5882,8 +8270,8 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -5892,8 +8280,8 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -5968,7 +8356,7 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="B1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -5997,68 +8385,68 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
-      <c r="C4" s="89" t="s">
+      <c r="C4" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89" t="s">
+      <c r="D4" s="76"/>
+      <c r="E4" s="76" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="77" t="s">
         <v>88</v>
       </c>
       <c r="C5" s="16">
         <v>90</v>
       </c>
       <c r="D5" s="16"/>
-      <c r="E5" s="82">
+      <c r="E5" s="70">
         <v>1056870</v>
       </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="80"/>
+      <c r="B6" s="69"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
-      <c r="E6" s="83"/>
+      <c r="E6" s="71"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="77" t="s">
         <v>88</v>
       </c>
       <c r="C7" s="16">
         <v>71</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="E7" s="82">
+      <c r="E7" s="70">
         <v>1397706</v>
       </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="77" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="82">
+      <c r="E8" s="70">
         <v>835212</v>
       </c>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="68">
         <v>61</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="82">
+      <c r="D9" s="68"/>
+      <c r="E9" s="70">
         <v>1730124</v>
       </c>
       <c r="F9" s="1"/>
@@ -6068,7 +8456,7 @@
       <c r="C10" s="16">
         <v>99</v>
       </c>
-      <c r="D10" s="81"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
@@ -6083,7 +8471,7 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B3:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
@@ -6093,184 +8481,184 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="D3" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="80" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="97">
+      <c r="C4" s="84">
         <v>4</v>
       </c>
-      <c r="D4" s="97">
+      <c r="D4" s="84">
         <v>99</v>
       </c>
-      <c r="E4" s="98">
+      <c r="E4" s="85">
         <v>1730124</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="97">
+      <c r="C5" s="84">
         <v>3</v>
       </c>
-      <c r="D5" s="97">
+      <c r="D5" s="84">
         <v>71</v>
       </c>
-      <c r="E5" s="98">
+      <c r="E5" s="85">
         <v>1218529</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="97">
+      <c r="C6" s="84">
         <v>2</v>
       </c>
-      <c r="D6" s="97">
+      <c r="D6" s="84">
         <v>82</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="85">
         <v>1579722</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="78">
         <v>9</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="78">
         <v>73</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="79">
         <v>1662496</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="95">
+      <c r="C8" s="82">
         <v>8</v>
       </c>
-      <c r="D8" s="95">
+      <c r="D8" s="82">
         <v>61</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="83">
         <v>835212</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="82" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="95">
+      <c r="C9" s="82">
         <v>7</v>
       </c>
-      <c r="D9" s="95">
+      <c r="D9" s="82">
         <v>63</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="83">
         <v>1994467</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="78">
         <v>6</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="78">
         <v>77</v>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="79">
         <v>1214288</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="78">
         <v>5</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="78">
         <v>79</v>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="79">
         <v>1986729</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="78">
         <v>12</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="78">
         <v>71</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="79">
         <v>1397706</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="78">
         <v>11</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="78">
         <v>66</v>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="79">
         <v>781503</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="78">
         <v>10</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="78">
         <v>90</v>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="79">
         <v>1056870</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="78">
         <v>1</v>
       </c>
-      <c r="D15" s="91">
+      <c r="D15" s="78">
         <v>67</v>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="79">
         <v>1335133</v>
       </c>
     </row>
@@ -6294,8 +8682,11 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A096CD0F-A30C-4A40-B434-AC75CD2815A7}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -6877,8 +9268,11 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B82D84-792E-4E99-A4B9-D8DF7CB43D7A}">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
   <dimension ref="A3:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -6887,7 +9281,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="87" t="s">
         <v>198</v>
       </c>
       <c r="B3" t="s">
@@ -6895,320 +9289,315 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="102"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="102">
+      <c r="B5">
         <v>646</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="89" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="102">
+      <c r="B6">
         <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="89" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="102">
+      <c r="B7">
         <v>638</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="89" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="102">
+      <c r="B8">
         <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="102">
+      <c r="B9">
         <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="102">
+      <c r="B10">
         <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="102">
+      <c r="B11">
         <v>3264</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="102"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="89" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="102">
+      <c r="B13">
         <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="89" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="102">
+      <c r="B14">
         <v>920</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="89" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="102">
+      <c r="B15">
         <v>662</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="102">
+      <c r="B16">
         <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="103" t="s">
+      <c r="A17" s="89" t="s">
         <v>147</v>
       </c>
-      <c r="B17" s="102">
+      <c r="B17">
         <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="89" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="102">
+      <c r="B18">
         <v>721</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="B19" s="102">
+      <c r="B19">
         <v>3640</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="101" t="s">
+      <c r="A20" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="102"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="103" t="s">
+      <c r="A21" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="102">
+      <c r="B21">
         <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="103" t="s">
+      <c r="A22" s="89" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="102">
+      <c r="B22">
         <v>951</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="103" t="s">
+      <c r="A23" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="102">
+      <c r="B23">
         <v>777</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="89" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="102">
+      <c r="B24">
         <v>382</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="103" t="s">
+      <c r="A25" s="89" t="s">
         <v>179</v>
       </c>
-      <c r="B25" s="102">
+      <c r="B25">
         <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="103" t="s">
+      <c r="A26" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="B26" s="102">
+      <c r="B26">
         <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="101" t="s">
+      <c r="A27" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="102">
+      <c r="B27">
         <v>3656</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="102"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="103" t="s">
+      <c r="A29" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="102">
+      <c r="B29">
         <v>690</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="102">
+      <c r="B30">
         <v>529</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="103" t="s">
+      <c r="A31" s="89" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="102">
+      <c r="B31">
         <v>884</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="103" t="s">
+      <c r="A32" s="89" t="s">
         <v>190</v>
       </c>
-      <c r="B32" s="102">
+      <c r="B32">
         <v>812</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="103" t="s">
+      <c r="A33" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="B33" s="102">
+      <c r="B33">
         <v>735</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="103" t="s">
+      <c r="A34" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="102">
+      <c r="B34">
         <v>843</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="101" t="s">
+      <c r="A35" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="B35" s="102">
+      <c r="B35">
         <v>4493</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="101" t="s">
+      <c r="A36" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="102"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="103" t="s">
+      <c r="A37" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="B37" s="102">
+      <c r="B37">
         <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="103" t="s">
+      <c r="A38" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="102">
+      <c r="B38">
         <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="103" t="s">
+      <c r="A39" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="102">
+      <c r="B39">
         <v>532</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="103" t="s">
+      <c r="A40" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="102">
+      <c r="B40">
         <v>615</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="103" t="s">
+      <c r="A41" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="B41" s="102">
+      <c r="B41">
         <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="103" t="s">
+      <c r="A42" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="102">
+      <c r="B42">
         <v>745</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="101" t="s">
+      <c r="A43" s="88" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="102">
+      <c r="B43">
         <v>3515</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="101" t="s">
+      <c r="A44" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="B44" s="102">
+      <c r="B44">
         <v>18568</v>
       </c>
     </row>
@@ -7227,8 +9616,11 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6366CB-3E1F-4683-8C9B-5C2B886A2ABA}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
     <col min="2" max="2" width="11.21875" customWidth="1"/>
@@ -7236,16 +9628,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="86" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="86" t="s">
         <v>128</v>
       </c>
     </row>
@@ -7681,84 +10073,231 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E6EE83-8E0E-4AD8-A50F-7D30CE59DC49}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3C97DA-5B59-4EF8-B2CD-9BCAFEBCB8FB}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A2:B29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="87" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="87" t="s">
         <v>198</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="B4" s="102">
+      <c r="B6">
         <v>3400</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="102">
+      <c r="B8">
         <v>3300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="88" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="88" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="88" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="102">
+      <c r="B12">
         <v>1800</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="88" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="88" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="88" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="88" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="88" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="88" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="88" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="88" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="102">
+      <c r="B22">
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="88" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="102">
+      <c r="B24">
         <v>2600</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="88" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="88" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="102">
+      <c r="B28">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="102">
-        <v>16600</v>
+      <c r="B29">
+        <v>55650</v>
       </c>
     </row>
   </sheetData>
@@ -7767,1103 +10306,12 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1955EDC7-B961-4B79-862B-56184D1214F1}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="102">
-        <v>2950</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="102">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="102">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="102">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="102">
-        <v>15500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06632B0F-E301-4613-876C-9996E1B47589}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53CA538-268F-4F51-BB9D-981C1ED66319}">
   <sheetPr>
-    <tabColor theme="3"/>
+    <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>34</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="8">
-        <v>51000</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="8">
-        <v>34500</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4">
-        <v>65</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="8">
-        <v>87750</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="4">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="8">
-        <v>31050</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="8">
-        <v>39600</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
-      </c>
-      <c r="D9" s="4">
-        <v>33</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="8">
-        <v>66000</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="1">
-        <f>COUNTIF(B4:B9, B12)</f>
-        <v>2</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="12">
-        <f>SUMIF(B4:B9,B15,G4:G9)</f>
-        <v>204750</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782665E2-70FB-49E0-9CE8-FD03474A8975}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="102">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="102">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="102">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="102">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>214</v>
-      </c>
-      <c r="B9" s="102">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="102">
-        <v>17150</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77255EB9-A96F-4454-95CC-2C0E7104C74B}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="102">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="102">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="102">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9" s="102">
-        <v>6400</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25245BDF-DBBD-4016-A6F3-C8695D55CF68}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="102">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="102">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="102">
-        <v>2950</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="102">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>217</v>
-      </c>
-      <c r="B8" s="102">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>211</v>
-      </c>
-      <c r="B9" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="B10" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
-        <v>229</v>
-      </c>
-      <c r="B11" s="102">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="102">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" s="102">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B15" s="102">
-        <v>22900</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB1DA1F-1B18-4336-B2F8-1A53211C66C7}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="101" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" s="102">
-        <v>3400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="102">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="102">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>218</v>
-      </c>
-      <c r="B7" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="102">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10" s="102">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="102">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" s="102">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="102">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="101" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="102">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="101" t="s">
-        <v>237</v>
-      </c>
-      <c r="B16" s="102">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B17" s="102">
-        <v>32750</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3C97DA-5B59-4EF8-B2CD-9BCAFEBCB8FB}">
-  <dimension ref="A2:B29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="102">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="102">
-        <v>3400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
-        <v>224</v>
-      </c>
-      <c r="B7" s="102">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="102">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
-        <v>227</v>
-      </c>
-      <c r="B9" s="102">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
-        <v>218</v>
-      </c>
-      <c r="B10" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
-        <v>215</v>
-      </c>
-      <c r="B11" s="102">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="102">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="102">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="102">
-        <v>2950</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="102">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="101" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" s="102">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="101" t="s">
-        <v>217</v>
-      </c>
-      <c r="B17" s="102">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="101" t="s">
-        <v>211</v>
-      </c>
-      <c r="B18" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="102">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="B20" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="101" t="s">
-        <v>209</v>
-      </c>
-      <c r="B21" s="102">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="101" t="s">
-        <v>205</v>
-      </c>
-      <c r="B22" s="102">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="101" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" s="102">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="101" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" s="102">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="101" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" s="102">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="102">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="101" t="s">
-        <v>231</v>
-      </c>
-      <c r="B27" s="102">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="101" t="s">
-        <v>237</v>
-      </c>
-      <c r="B28" s="102">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="101" t="s">
-        <v>197</v>
-      </c>
-      <c r="B29" s="102">
-        <v>55650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53CA538-268F-4F51-BB9D-981C1ED66319}">
   <dimension ref="B3:N30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -8876,40 +10324,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="104" t="s">
+      <c r="D3" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E3" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="104" t="s">
+      <c r="F3" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="I3" s="104" t="s">
+      <c r="I3" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J3" s="104" t="s">
+      <c r="J3" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="K3" s="104" t="s">
+      <c r="K3" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="L3" s="104" t="s">
+      <c r="L3" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="104" t="s">
+      <c r="M3" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="104" t="s">
+      <c r="N3" s="90" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9021,22 +10469,22 @@
       <c r="G8" s="16">
         <v>2500</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J8" s="104" t="s">
+      <c r="J8" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="K8" s="104" t="s">
+      <c r="K8" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="L8" s="104" t="s">
+      <c r="L8" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="104" t="s">
+      <c r="M8" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="N8" s="104" t="s">
+      <c r="N8" s="90" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9215,22 +10663,22 @@
       <c r="G15" s="16">
         <v>2600</v>
       </c>
-      <c r="I15" s="104" t="s">
+      <c r="I15" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J15" s="104" t="s">
+      <c r="J15" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="104" t="s">
+      <c r="K15" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="L15" s="104" t="s">
+      <c r="L15" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="104" t="s">
+      <c r="M15" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="N15" s="104" t="s">
+      <c r="N15" s="90" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9523,22 +10971,22 @@
       <c r="G25" s="16">
         <v>3300</v>
       </c>
-      <c r="I25" s="104" t="s">
+      <c r="I25" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="J25" s="104" t="s">
+      <c r="J25" s="90" t="s">
         <v>201</v>
       </c>
-      <c r="K25" s="104" t="s">
+      <c r="K25" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="L25" s="104" t="s">
+      <c r="L25" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="M25" s="104" t="s">
+      <c r="M25" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="N25" s="104" t="s">
+      <c r="N25" s="90" t="s">
         <v>204</v>
       </c>
     </row>
@@ -9679,6 +11127,1596 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06632B0F-E301-4613-876C-9996E1B47589}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>34</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8">
+        <v>51000</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8">
+        <v>34500</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>65</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8">
+        <v>87750</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="8">
+        <v>31050</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="8">
+        <v>39600</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>33</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="8">
+        <v>66000</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1">
+        <f>COUNTIF(B4:B9, B12)</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="12">
+        <f>SUMIF(B4:B9,B15,G4:G9)</f>
+        <v>204750</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92490FC8-7AB9-4E9D-A7BA-53A598404159}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="B4:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="47">
+        <v>99</v>
+      </c>
+      <c r="D5" s="103">
+        <v>1730124</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="47">
+        <v>71</v>
+      </c>
+      <c r="D6" s="103">
+        <v>1218529</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="47">
+        <v>82</v>
+      </c>
+      <c r="D7" s="103">
+        <v>1579722</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="81" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="78">
+        <v>73</v>
+      </c>
+      <c r="D8" s="104">
+        <v>1662496</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="47">
+        <v>61</v>
+      </c>
+      <c r="D9" s="103">
+        <v>835212</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="47">
+        <v>63</v>
+      </c>
+      <c r="D10" s="103">
+        <v>1994467</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="78">
+        <v>77</v>
+      </c>
+      <c r="D11" s="104">
+        <v>1214288</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="78">
+        <v>79</v>
+      </c>
+      <c r="D12" s="104">
+        <v>1986729</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="78">
+        <v>71</v>
+      </c>
+      <c r="D13" s="104">
+        <v>1397706</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="81" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="78">
+        <v>66</v>
+      </c>
+      <c r="D14" s="104">
+        <v>781503</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="78">
+        <v>90</v>
+      </c>
+      <c r="D15" s="104">
+        <v>1056870</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="78">
+        <v>67</v>
+      </c>
+      <c r="D16" s="104">
+        <v>1335133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DC53E2-CEC6-4A6B-8A6E-FA886FF2F568}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A2:I32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="106" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="106" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" s="106" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" s="106" t="s">
+        <v>241</v>
+      </c>
+      <c r="G2" s="106" t="s">
+        <v>242</v>
+      </c>
+      <c r="H2" s="106" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" s="106" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="107" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="108">
+        <v>90</v>
+      </c>
+      <c r="C3" s="108">
+        <v>198670</v>
+      </c>
+      <c r="D3" s="108">
+        <v>357543</v>
+      </c>
+      <c r="E3" s="108">
+        <v>291605</v>
+      </c>
+      <c r="F3" s="108">
+        <v>171139</v>
+      </c>
+      <c r="G3" s="108">
+        <v>604102</v>
+      </c>
+      <c r="H3" s="108">
+        <v>312159</v>
+      </c>
+      <c r="I3" s="108">
+        <v>368737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="108">
+        <v>71</v>
+      </c>
+      <c r="C4" s="108">
+        <v>149700</v>
+      </c>
+      <c r="D4" s="108">
+        <v>674870</v>
+      </c>
+      <c r="E4" s="108">
+        <v>339099</v>
+      </c>
+      <c r="F4" s="108">
+        <v>432496</v>
+      </c>
+      <c r="G4" s="108">
+        <v>800102</v>
+      </c>
+      <c r="H4" s="108">
+        <v>246213</v>
+      </c>
+      <c r="I4" s="108">
+        <v>1911843</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="107" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="108">
+        <v>61</v>
+      </c>
+      <c r="C5" s="108">
+        <v>853212</v>
+      </c>
+      <c r="D5" s="108">
+        <v>345309</v>
+      </c>
+      <c r="E5" s="108">
+        <v>288767</v>
+      </c>
+      <c r="F5" s="108">
+        <v>222390</v>
+      </c>
+      <c r="G5" s="108">
+        <v>338695</v>
+      </c>
+      <c r="H5" s="108">
+        <v>756039</v>
+      </c>
+      <c r="I5" s="108">
+        <v>175603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="107" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="108">
+        <v>99</v>
+      </c>
+      <c r="C6" s="108">
+        <v>1179124</v>
+      </c>
+      <c r="D6" s="108">
+        <v>761403</v>
+      </c>
+      <c r="E6" s="108">
+        <v>182711</v>
+      </c>
+      <c r="F6" s="108">
+        <v>920389</v>
+      </c>
+      <c r="G6" s="108">
+        <v>348750</v>
+      </c>
+      <c r="H6" s="108">
+        <v>347620</v>
+      </c>
+      <c r="I6" s="108">
+        <v>371823</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="107" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="108">
+        <v>73</v>
+      </c>
+      <c r="C7" s="108">
+        <v>1662496</v>
+      </c>
+      <c r="D7" s="108">
+        <v>461672</v>
+      </c>
+      <c r="E7" s="108">
+        <v>386391</v>
+      </c>
+      <c r="F7" s="108">
+        <v>118392</v>
+      </c>
+      <c r="G7" s="108">
+        <v>254943</v>
+      </c>
+      <c r="H7" s="108">
+        <v>218947</v>
+      </c>
+      <c r="I7" s="108">
+        <v>1060171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="107" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="108">
+        <v>81</v>
+      </c>
+      <c r="C8" s="108">
+        <v>1214288</v>
+      </c>
+      <c r="D8" s="108">
+        <v>499919</v>
+      </c>
+      <c r="E8" s="108">
+        <v>272297</v>
+      </c>
+      <c r="F8" s="108">
+        <v>153321</v>
+      </c>
+      <c r="G8" s="108">
+        <v>967214</v>
+      </c>
+      <c r="H8" s="108">
+        <v>547596</v>
+      </c>
+      <c r="I8" s="108">
+        <v>132655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="108">
+        <v>77</v>
+      </c>
+      <c r="C9" s="108">
+        <v>1218529</v>
+      </c>
+      <c r="D9" s="108">
+        <v>289899</v>
+      </c>
+      <c r="E9" s="108">
+        <v>407553</v>
+      </c>
+      <c r="F9" s="108">
+        <v>176404</v>
+      </c>
+      <c r="G9" s="108">
+        <v>259826</v>
+      </c>
+      <c r="H9" s="108">
+        <v>311507</v>
+      </c>
+      <c r="I9" s="108">
+        <v>164060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="108">
+        <v>79</v>
+      </c>
+      <c r="C10" s="108">
+        <v>1986729</v>
+      </c>
+      <c r="D10" s="108">
+        <v>343302</v>
+      </c>
+      <c r="E10" s="108">
+        <v>497188</v>
+      </c>
+      <c r="F10" s="108">
+        <v>251054</v>
+      </c>
+      <c r="G10" s="108">
+        <v>424327</v>
+      </c>
+      <c r="H10" s="108">
+        <v>764158</v>
+      </c>
+      <c r="I10" s="108">
+        <v>244159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="107" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="108">
+        <v>65</v>
+      </c>
+      <c r="C11" s="108">
+        <v>1335133</v>
+      </c>
+      <c r="D11" s="108">
+        <v>492907</v>
+      </c>
+      <c r="E11" s="108">
+        <v>480311</v>
+      </c>
+      <c r="F11" s="108">
+        <v>278081</v>
+      </c>
+      <c r="G11" s="108">
+        <v>377185</v>
+      </c>
+      <c r="H11" s="108">
+        <v>425849</v>
+      </c>
+      <c r="I11" s="108">
+        <v>386372</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="107" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="108">
+        <v>82</v>
+      </c>
+      <c r="C12" s="108">
+        <v>781503</v>
+      </c>
+      <c r="D12" s="108">
+        <v>151520</v>
+      </c>
+      <c r="E12" s="108">
+        <v>497039</v>
+      </c>
+      <c r="F12" s="108">
+        <v>256220</v>
+      </c>
+      <c r="G12" s="108">
+        <v>401064</v>
+      </c>
+      <c r="H12" s="108">
+        <v>321636</v>
+      </c>
+      <c r="I12" s="108">
+        <v>996777</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="107" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="108">
+        <v>84</v>
+      </c>
+      <c r="C13" s="108">
+        <v>1579722</v>
+      </c>
+      <c r="D13" s="108">
+        <v>183505</v>
+      </c>
+      <c r="E13" s="108">
+        <v>151371</v>
+      </c>
+      <c r="F13" s="108">
+        <v>866004</v>
+      </c>
+      <c r="G13" s="108">
+        <v>156574</v>
+      </c>
+      <c r="H13" s="108">
+        <v>425496</v>
+      </c>
+      <c r="I13" s="108">
+        <v>336632</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="107" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="108">
+        <v>78</v>
+      </c>
+      <c r="C14" s="108">
+        <v>1767198</v>
+      </c>
+      <c r="D14" s="108">
+        <v>249994</v>
+      </c>
+      <c r="E14" s="108">
+        <v>452721</v>
+      </c>
+      <c r="F14" s="108">
+        <v>205865</v>
+      </c>
+      <c r="G14" s="108">
+        <v>342787</v>
+      </c>
+      <c r="H14" s="108">
+        <v>234396</v>
+      </c>
+      <c r="I14" s="108">
+        <v>449042</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="107" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="108">
+        <v>72</v>
+      </c>
+      <c r="C15" s="108">
+        <v>1384234</v>
+      </c>
+      <c r="D15" s="108">
+        <v>315206</v>
+      </c>
+      <c r="E15" s="108">
+        <v>151711</v>
+      </c>
+      <c r="F15" s="108">
+        <v>328798</v>
+      </c>
+      <c r="G15" s="108">
+        <v>382009</v>
+      </c>
+      <c r="H15" s="108">
+        <v>156059</v>
+      </c>
+      <c r="I15" s="108">
+        <v>623043</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="107" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="108">
+        <v>91</v>
+      </c>
+      <c r="C16" s="108">
+        <v>1474996</v>
+      </c>
+      <c r="D16" s="108">
+        <v>306715</v>
+      </c>
+      <c r="E16" s="108">
+        <v>330724</v>
+      </c>
+      <c r="F16" s="108">
+        <v>210003</v>
+      </c>
+      <c r="G16" s="108">
+        <v>161047</v>
+      </c>
+      <c r="H16" s="108">
+        <v>281608</v>
+      </c>
+      <c r="I16" s="108">
+        <v>344815</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="107" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="108">
+        <v>83</v>
+      </c>
+      <c r="C17" s="108">
+        <v>621782</v>
+      </c>
+      <c r="D17" s="108">
+        <v>264614</v>
+      </c>
+      <c r="E17" s="108">
+        <v>465767</v>
+      </c>
+      <c r="F17" s="108">
+        <v>304212</v>
+      </c>
+      <c r="G17" s="108">
+        <v>113617</v>
+      </c>
+      <c r="H17" s="108">
+        <v>292459</v>
+      </c>
+      <c r="I17" s="108">
+        <v>277520</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="107" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="108">
+        <v>100</v>
+      </c>
+      <c r="C18" s="108">
+        <v>1236325</v>
+      </c>
+      <c r="D18" s="108">
+        <v>491725</v>
+      </c>
+      <c r="E18" s="108">
+        <v>402207</v>
+      </c>
+      <c r="F18" s="108">
+        <v>230596</v>
+      </c>
+      <c r="G18" s="108">
+        <v>136072</v>
+      </c>
+      <c r="H18" s="108">
+        <v>181773</v>
+      </c>
+      <c r="I18" s="108">
+        <v>188940</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="107" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="108">
+        <v>68</v>
+      </c>
+      <c r="C19" s="108">
+        <v>1637656</v>
+      </c>
+      <c r="D19" s="108">
+        <v>612599</v>
+      </c>
+      <c r="E19" s="108">
+        <v>237699</v>
+      </c>
+      <c r="F19" s="108">
+        <v>650446</v>
+      </c>
+      <c r="G19" s="108">
+        <v>364484</v>
+      </c>
+      <c r="H19" s="108">
+        <v>194247</v>
+      </c>
+      <c r="I19" s="108">
+        <v>163087</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="107" t="s">
+        <v>250</v>
+      </c>
+      <c r="B20" s="108">
+        <v>97</v>
+      </c>
+      <c r="C20" s="108">
+        <v>1875319</v>
+      </c>
+      <c r="D20" s="108">
+        <v>187094</v>
+      </c>
+      <c r="E20" s="108">
+        <v>583669</v>
+      </c>
+      <c r="F20" s="108">
+        <v>240172</v>
+      </c>
+      <c r="G20" s="108">
+        <v>153570</v>
+      </c>
+      <c r="H20" s="108">
+        <v>194258</v>
+      </c>
+      <c r="I20" s="108">
+        <v>666713</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" s="108">
+        <v>75</v>
+      </c>
+      <c r="C21" s="108">
+        <v>1965307</v>
+      </c>
+      <c r="D21" s="108">
+        <v>172120</v>
+      </c>
+      <c r="E21" s="108">
+        <v>467938</v>
+      </c>
+      <c r="F21" s="108">
+        <v>278500</v>
+      </c>
+      <c r="G21" s="108">
+        <v>218499</v>
+      </c>
+      <c r="H21" s="108">
+        <v>179266</v>
+      </c>
+      <c r="I21" s="108">
+        <v>329591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="107" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="108">
+        <v>88</v>
+      </c>
+      <c r="C22" s="108">
+        <v>609184</v>
+      </c>
+      <c r="D22" s="108">
+        <v>191843</v>
+      </c>
+      <c r="E22" s="108">
+        <v>456062</v>
+      </c>
+      <c r="F22" s="108">
+        <v>463907</v>
+      </c>
+      <c r="G22" s="108">
+        <v>425282</v>
+      </c>
+      <c r="H22" s="108">
+        <v>104199</v>
+      </c>
+      <c r="I22" s="108">
+        <v>1235300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="107" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="108">
+        <v>92</v>
+      </c>
+      <c r="C23" s="108">
+        <v>1459032</v>
+      </c>
+      <c r="D23" s="108">
+        <v>461690</v>
+      </c>
+      <c r="E23" s="108">
+        <v>291838</v>
+      </c>
+      <c r="F23" s="108">
+        <v>489741</v>
+      </c>
+      <c r="G23" s="108">
+        <v>405999</v>
+      </c>
+      <c r="H23" s="108">
+        <v>420214</v>
+      </c>
+      <c r="I23" s="108">
+        <v>910261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="107" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="108">
+        <v>69</v>
+      </c>
+      <c r="C24" s="108">
+        <v>1484826</v>
+      </c>
+      <c r="D24" s="108">
+        <v>307171</v>
+      </c>
+      <c r="E24" s="108">
+        <v>385839</v>
+      </c>
+      <c r="F24" s="108">
+        <v>684234</v>
+      </c>
+      <c r="G24" s="108">
+        <v>540136</v>
+      </c>
+      <c r="H24" s="108">
+        <v>757088</v>
+      </c>
+      <c r="I24" s="108">
+        <v>435623</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="107" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="108">
+        <v>95</v>
+      </c>
+      <c r="C25" s="108">
+        <v>1584799</v>
+      </c>
+      <c r="D25" s="108">
+        <v>293974</v>
+      </c>
+      <c r="E25" s="108">
+        <v>459629</v>
+      </c>
+      <c r="F25" s="108">
+        <v>116621</v>
+      </c>
+      <c r="G25" s="108">
+        <v>170745</v>
+      </c>
+      <c r="H25" s="108">
+        <v>240954</v>
+      </c>
+      <c r="I25" s="108">
+        <v>246735</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="107" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="108">
+        <v>87</v>
+      </c>
+      <c r="C26" s="108">
+        <v>1237610</v>
+      </c>
+      <c r="D26" s="108">
+        <v>131279</v>
+      </c>
+      <c r="E26" s="108">
+        <v>351328</v>
+      </c>
+      <c r="F26" s="108">
+        <v>178034</v>
+      </c>
+      <c r="G26" s="108">
+        <v>345447</v>
+      </c>
+      <c r="H26" s="108">
+        <v>306294</v>
+      </c>
+      <c r="I26" s="108">
+        <v>336852</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="107" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="108">
+        <v>80</v>
+      </c>
+      <c r="C27" s="108">
+        <v>1203588</v>
+      </c>
+      <c r="D27" s="108">
+        <v>800097</v>
+      </c>
+      <c r="E27" s="108">
+        <v>149667</v>
+      </c>
+      <c r="F27" s="108">
+        <v>134347</v>
+      </c>
+      <c r="G27" s="108">
+        <v>731147</v>
+      </c>
+      <c r="H27" s="108">
+        <v>321149</v>
+      </c>
+      <c r="I27" s="108">
+        <v>457816</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="107" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="108">
+        <v>76</v>
+      </c>
+      <c r="C28" s="108">
+        <v>1403006</v>
+      </c>
+      <c r="D28" s="108">
+        <v>632560</v>
+      </c>
+      <c r="E28" s="108">
+        <v>218457</v>
+      </c>
+      <c r="F28" s="108">
+        <v>231718</v>
+      </c>
+      <c r="G28" s="108">
+        <v>234513</v>
+      </c>
+      <c r="H28" s="108">
+        <v>200687</v>
+      </c>
+      <c r="I28" s="108">
+        <v>1450244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="107" t="s">
+        <v>259</v>
+      </c>
+      <c r="B29" s="108">
+        <v>89</v>
+      </c>
+      <c r="C29" s="108">
+        <v>683504</v>
+      </c>
+      <c r="D29" s="108">
+        <v>265909</v>
+      </c>
+      <c r="E29" s="108">
+        <v>262471</v>
+      </c>
+      <c r="F29" s="108">
+        <v>347820</v>
+      </c>
+      <c r="G29" s="108">
+        <v>315247</v>
+      </c>
+      <c r="H29" s="108">
+        <v>206784</v>
+      </c>
+      <c r="I29" s="108">
+        <v>368529</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="107" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="108">
+        <v>93</v>
+      </c>
+      <c r="C30" s="108">
+        <v>1236500</v>
+      </c>
+      <c r="D30" s="108">
+        <v>420118</v>
+      </c>
+      <c r="E30" s="108">
+        <v>401882</v>
+      </c>
+      <c r="F30" s="108">
+        <v>291365</v>
+      </c>
+      <c r="G30" s="108">
+        <v>501245</v>
+      </c>
+      <c r="H30" s="108">
+        <v>356921</v>
+      </c>
+      <c r="I30" s="108">
+        <v>820145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="107" t="s">
+        <v>261</v>
+      </c>
+      <c r="B31" s="108">
+        <v>85</v>
+      </c>
+      <c r="C31" s="108">
+        <v>1754788</v>
+      </c>
+      <c r="D31" s="108">
+        <v>318774</v>
+      </c>
+      <c r="E31" s="108">
+        <v>289634</v>
+      </c>
+      <c r="F31" s="108">
+        <v>514890</v>
+      </c>
+      <c r="G31" s="108">
+        <v>682114</v>
+      </c>
+      <c r="H31" s="108">
+        <v>490633</v>
+      </c>
+      <c r="I31" s="108">
+        <v>390588</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="107" t="s">
+        <v>262</v>
+      </c>
+      <c r="B32" s="108">
+        <v>70</v>
+      </c>
+      <c r="C32" s="108">
+        <v>739220</v>
+      </c>
+      <c r="D32" s="108">
+        <v>763331</v>
+      </c>
+      <c r="E32" s="108">
+        <v>126787</v>
+      </c>
+      <c r="F32" s="108">
+        <v>872674</v>
+      </c>
+      <c r="G32" s="108">
+        <v>313218</v>
+      </c>
+      <c r="H32" s="108">
+        <v>393193</v>
+      </c>
+      <c r="I32" s="108">
+        <v>1879246</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ABE0D0-45BC-4EBA-9914-5EA1E6D466A8}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="B2:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="10" width="25.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="121" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="121" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="121" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="122" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="47">
+        <v>19</v>
+      </c>
+      <c r="D4" s="115">
+        <v>27</v>
+      </c>
+      <c r="E4" s="47">
+        <v>46</v>
+      </c>
+      <c r="J4" s="122" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="47" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="47">
+        <v>37</v>
+      </c>
+      <c r="D5" s="115">
+        <v>91</v>
+      </c>
+      <c r="E5" s="47">
+        <v>128</v>
+      </c>
+      <c r="J5" s="122" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="47">
+        <v>49</v>
+      </c>
+      <c r="D6" s="115">
+        <v>68</v>
+      </c>
+      <c r="E6" s="47">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="47">
+        <v>48</v>
+      </c>
+      <c r="D7" s="115">
+        <v>62</v>
+      </c>
+      <c r="E7" s="47">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="78">
+        <v>47</v>
+      </c>
+      <c r="D8" s="116">
+        <v>69</v>
+      </c>
+      <c r="E8" s="47">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="109"/>
+      <c r="C9" s="109">
+        <f t="shared" ref="C9:D9" si="0">SUM(C4:C8)</f>
+        <v>200</v>
+      </c>
+      <c r="D9" s="114">
+        <f t="shared" si="0"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="109"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="110"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="111"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="113"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="111"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="113"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="111"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="113"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="111"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="113"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="113"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2859D02-BE31-4F09-AAEE-A17B563D2BCF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9689,11 +12727,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A2:G9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -9830,7 +12869,7 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -10190,7 +13229,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B4:H15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
@@ -10459,7 +13498,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
@@ -10825,7 +13864,7 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -11179,10 +14218,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1">
-        <f>_xlfn.XLOOKUP(G5,B5:B14,E5:E14,0)</f>
-        <v>0</v>
-      </c>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -11199,7 +14235,7 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A4:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -11211,10 +14247,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="93"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="47" t="s">
@@ -11263,7 +14299,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
@@ -11274,13 +14310,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
